--- a/research/traditional_assets/database/data/romania/romania_food_wholesalers.xlsx
+++ b/research/traditional_assets/database/data/romania/romania_food_wholesalers.xlsx
@@ -1272,7 +1272,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1409,22 +1409,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.08244406461945282</v>
+        <v>0.08234995411606168</v>
       </c>
       <c r="C2">
-        <v>17.7</v>
+        <v>17.52463561932679</v>
       </c>
       <c r="D2">
-        <v>6.6</v>
+        <v>6.601635619326792</v>
       </c>
       <c r="E2">
-        <v>0</v>
+        <v>0.177</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>0.177</v>
       </c>
       <c r="G2">
         <v>11.1</v>
@@ -1445,28 +1445,28 @@
         <v>4.074</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>0.008903099999999999</v>
       </c>
       <c r="N2">
-        <v>4.074</v>
+        <v>4.065096899999999</v>
       </c>
       <c r="O2">
-        <v>0.65184</v>
+        <v>0.6504155039999999</v>
       </c>
       <c r="P2">
-        <v>3.42216</v>
+        <v>3.414681396</v>
       </c>
       <c r="Q2">
-        <v>3.56816</v>
+        <v>3.560681396</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.08244406461945282</v>
+        <v>0.08275498395561787</v>
       </c>
       <c r="T2">
-        <v>0.5044193424952811</v>
+        <v>0.5086992641891804</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1483,7 +1483,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>457.5934225157529</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1491,22 +1491,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.08234995411606168</v>
+        <v>0.08225584361267058</v>
       </c>
       <c r="C3">
-        <v>17.52463561932679</v>
+        <v>17.34927204953653</v>
       </c>
       <c r="D3">
-        <v>6.601635619326792</v>
+        <v>6.603272049536531</v>
       </c>
       <c r="E3">
-        <v>0.177</v>
+        <v>0.354</v>
       </c>
       <c r="F3">
-        <v>0.177</v>
+        <v>0.354</v>
       </c>
       <c r="G3">
         <v>11.1</v>
@@ -1527,28 +1527,28 @@
         <v>4.074</v>
       </c>
       <c r="M3">
-        <v>0.008903099999999999</v>
+        <v>0.0178062</v>
       </c>
       <c r="N3">
-        <v>4.065096899999999</v>
+        <v>4.0561938</v>
       </c>
       <c r="O3">
-        <v>0.6504155039999999</v>
+        <v>0.648991008</v>
       </c>
       <c r="P3">
-        <v>3.414681396</v>
+        <v>3.407202792</v>
       </c>
       <c r="Q3">
-        <v>3.560681396</v>
+        <v>3.553202792</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.08275498395561787</v>
+        <v>0.08307224858435773</v>
       </c>
       <c r="T3">
-        <v>0.5086992641891804</v>
+        <v>0.5130665312237717</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1565,7 +1565,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>457.5934225157529</v>
+        <v>228.7967112578765</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1573,22 +1573,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.08225584361267058</v>
+        <v>0.08216173310927945</v>
       </c>
       <c r="C4">
-        <v>17.34927204953653</v>
+        <v>17.17390929123238</v>
       </c>
       <c r="D4">
-        <v>6.603272049536531</v>
+        <v>6.604909291232381</v>
       </c>
       <c r="E4">
-        <v>0.354</v>
+        <v>0.5309999999999999</v>
       </c>
       <c r="F4">
-        <v>0.354</v>
+        <v>0.5309999999999999</v>
       </c>
       <c r="G4">
         <v>11.1</v>
@@ -1609,28 +1609,28 @@
         <v>4.074</v>
       </c>
       <c r="M4">
-        <v>0.0178062</v>
+        <v>0.02670929999999999</v>
       </c>
       <c r="N4">
-        <v>4.0561938</v>
+        <v>4.0472907</v>
       </c>
       <c r="O4">
-        <v>0.648991008</v>
+        <v>0.6475665119999999</v>
       </c>
       <c r="P4">
-        <v>3.407202792</v>
+        <v>3.399724188</v>
       </c>
       <c r="Q4">
-        <v>3.553202792</v>
+        <v>3.545724187999999</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.08307224858435773</v>
+        <v>0.08339605475183448</v>
       </c>
       <c r="T4">
-        <v>0.5130665312237717</v>
+        <v>0.5175238450013441</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1647,7 +1647,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>228.7967112578765</v>
+        <v>152.5311408385843</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1655,22 +1655,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.08216173310927945</v>
+        <v>0.08206762260588832</v>
       </c>
       <c r="C5">
-        <v>17.17390929123238</v>
+        <v>16.9985473450181</v>
       </c>
       <c r="D5">
-        <v>6.604909291232381</v>
+        <v>6.606547345018098</v>
       </c>
       <c r="E5">
-        <v>0.5309999999999999</v>
+        <v>0.708</v>
       </c>
       <c r="F5">
-        <v>0.5309999999999999</v>
+        <v>0.708</v>
       </c>
       <c r="G5">
         <v>11.1</v>
@@ -1691,28 +1691,28 @@
         <v>4.074</v>
       </c>
       <c r="M5">
-        <v>0.02670929999999999</v>
+        <v>0.0356124</v>
       </c>
       <c r="N5">
-        <v>4.0472907</v>
+        <v>4.0383876</v>
       </c>
       <c r="O5">
-        <v>0.6475665119999999</v>
+        <v>0.646142016</v>
       </c>
       <c r="P5">
-        <v>3.399724188</v>
+        <v>3.392245584</v>
       </c>
       <c r="Q5">
-        <v>3.545724187999999</v>
+        <v>3.538245584</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.08339605475183448</v>
+        <v>0.08372660688113367</v>
       </c>
       <c r="T5">
-        <v>0.5175238450013441</v>
+        <v>0.5220740194826159</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1729,7 +1729,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>152.5311408385843</v>
+        <v>114.3983556289382</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1737,22 +1737,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.08206762260588832</v>
+        <v>0.08197351210249722</v>
       </c>
       <c r="C6">
-        <v>16.9985473450181</v>
+        <v>16.82318621149804</v>
       </c>
       <c r="D6">
-        <v>6.606547345018098</v>
+        <v>6.608186211498041</v>
       </c>
       <c r="E6">
-        <v>0.708</v>
+        <v>0.885</v>
       </c>
       <c r="F6">
-        <v>0.708</v>
+        <v>0.885</v>
       </c>
       <c r="G6">
         <v>11.1</v>
@@ -1773,28 +1773,28 @@
         <v>4.074</v>
       </c>
       <c r="M6">
-        <v>0.0356124</v>
+        <v>0.0445155</v>
       </c>
       <c r="N6">
-        <v>4.0383876</v>
+        <v>4.0294845</v>
       </c>
       <c r="O6">
-        <v>0.646142016</v>
+        <v>0.6447175199999999</v>
       </c>
       <c r="P6">
-        <v>3.392245584</v>
+        <v>3.38476698</v>
       </c>
       <c r="Q6">
-        <v>3.538245584</v>
+        <v>3.53076698</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.08372660688113367</v>
+        <v>0.08406411800262864</v>
       </c>
       <c r="T6">
-        <v>0.5220740194826159</v>
+        <v>0.526719987110862</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -1811,7 +1811,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>114.3983556289382</v>
+        <v>91.51868450315058</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1819,22 +1819,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.08197351210249722</v>
+        <v>0.08187940159910607</v>
       </c>
       <c r="C7">
-        <v>16.82318621149804</v>
+        <v>16.64782589127717</v>
       </c>
       <c r="D7">
-        <v>6.608186211498041</v>
+        <v>6.609825891277171</v>
       </c>
       <c r="E7">
-        <v>0.885</v>
+        <v>1.062</v>
       </c>
       <c r="F7">
-        <v>0.885</v>
+        <v>1.062</v>
       </c>
       <c r="G7">
         <v>11.1</v>
@@ -1855,28 +1855,28 @@
         <v>4.074</v>
       </c>
       <c r="M7">
-        <v>0.0445155</v>
+        <v>0.0534186</v>
       </c>
       <c r="N7">
-        <v>4.0294845</v>
+        <v>4.0205814</v>
       </c>
       <c r="O7">
-        <v>0.6447175199999999</v>
+        <v>0.643293024</v>
       </c>
       <c r="P7">
-        <v>3.38476698</v>
+        <v>3.377288376</v>
       </c>
       <c r="Q7">
-        <v>3.53076698</v>
+        <v>3.523288376</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.08406411800262864</v>
+        <v>0.08440881021181497</v>
       </c>
       <c r="T7">
-        <v>0.526719987110862</v>
+        <v>0.531464805114177</v>
       </c>
       <c r="U7">
         <v>0.0503</v>
@@ -1893,7 +1893,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>91.51868450315058</v>
+        <v>76.26557041929216</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1901,22 +1901,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.08187940159910607</v>
+        <v>0.08178529109571495</v>
       </c>
       <c r="C8">
-        <v>16.64782589127717</v>
+        <v>16.47246638496104</v>
       </c>
       <c r="D8">
-        <v>6.609825891277171</v>
+        <v>6.611466384961042</v>
       </c>
       <c r="E8">
-        <v>1.062</v>
+        <v>1.239</v>
       </c>
       <c r="F8">
-        <v>1.062</v>
+        <v>1.239</v>
       </c>
       <c r="G8">
         <v>11.1</v>
@@ -1937,28 +1937,28 @@
         <v>4.074</v>
       </c>
       <c r="M8">
-        <v>0.05341859999999999</v>
+        <v>0.06232169999999999</v>
       </c>
       <c r="N8">
-        <v>4.0205814</v>
+        <v>4.0116783</v>
       </c>
       <c r="O8">
-        <v>0.643293024</v>
+        <v>0.6418685279999999</v>
       </c>
       <c r="P8">
-        <v>3.377288376</v>
+        <v>3.369809772</v>
       </c>
       <c r="Q8">
-        <v>3.523288376</v>
+        <v>3.515809772</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.08440881021181497</v>
+        <v>0.08476091515668274</v>
       </c>
       <c r="T8">
-        <v>0.531464805114177</v>
+        <v>0.5363116622143376</v>
       </c>
       <c r="U8">
         <v>0.0503</v>
@@ -1975,7 +1975,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>76.26557041929217</v>
+        <v>65.37048893082185</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1983,22 +1983,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.08178529109571495</v>
+        <v>0.08169118059232383</v>
       </c>
       <c r="C9">
-        <v>16.47246638496104</v>
+        <v>16.29710769315582</v>
       </c>
       <c r="D9">
-        <v>6.611466384961042</v>
+        <v>6.613107693155816</v>
       </c>
       <c r="E9">
-        <v>1.239</v>
+        <v>1.416</v>
       </c>
       <c r="F9">
-        <v>1.239</v>
+        <v>1.416</v>
       </c>
       <c r="G9">
         <v>11.1</v>
@@ -2019,28 +2019,28 @@
         <v>4.074</v>
       </c>
       <c r="M9">
-        <v>0.0623217</v>
+        <v>0.07122479999999999</v>
       </c>
       <c r="N9">
-        <v>4.0116783</v>
+        <v>4.002775199999999</v>
       </c>
       <c r="O9">
-        <v>0.6418685279999999</v>
+        <v>0.6404440319999999</v>
       </c>
       <c r="P9">
-        <v>3.369809772</v>
+        <v>3.362331167999999</v>
       </c>
       <c r="Q9">
-        <v>3.515809772</v>
+        <v>3.508331167999999</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.08476091515668274</v>
+        <v>0.08512067455687372</v>
       </c>
       <c r="T9">
-        <v>0.5363116622143376</v>
+        <v>0.5412638857731973</v>
       </c>
       <c r="U9">
         <v>0.0503</v>
@@ -2057,7 +2057,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>65.37048893082185</v>
+        <v>57.19917781446912</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2065,22 +2065,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.08169118059232383</v>
+        <v>0.0815970700889327</v>
       </c>
       <c r="C10">
-        <v>16.29710769315582</v>
+        <v>16.12174981646825</v>
       </c>
       <c r="D10">
-        <v>6.613107693155816</v>
+        <v>6.614749816468254</v>
       </c>
       <c r="E10">
-        <v>1.416</v>
+        <v>1.593</v>
       </c>
       <c r="F10">
-        <v>1.416</v>
+        <v>1.593</v>
       </c>
       <c r="G10">
         <v>11.1</v>
@@ -2101,28 +2101,28 @@
         <v>4.074</v>
       </c>
       <c r="M10">
-        <v>0.07122479999999999</v>
+        <v>0.08012789999999999</v>
       </c>
       <c r="N10">
-        <v>4.002775199999999</v>
+        <v>3.9938721</v>
       </c>
       <c r="O10">
-        <v>0.6404440319999999</v>
+        <v>0.6390195360000001</v>
       </c>
       <c r="P10">
-        <v>3.362331167999999</v>
+        <v>3.354852564</v>
       </c>
       <c r="Q10">
-        <v>3.508331167999999</v>
+        <v>3.500852564</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.08512067455687372</v>
+        <v>0.0854883407570689</v>
       </c>
       <c r="T10">
-        <v>0.5412638857731973</v>
+        <v>0.5463249494102737</v>
       </c>
       <c r="U10">
         <v>0.0503</v>
@@ -2139,7 +2139,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>57.19917781446912</v>
+        <v>50.84371361286144</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2147,22 +2147,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.0815970700889327</v>
+        <v>0.08150295958554156</v>
       </c>
       <c r="C11">
-        <v>16.12174981646825</v>
+        <v>15.94639275550572</v>
       </c>
       <c r="D11">
-        <v>6.614749816468254</v>
+        <v>6.616392755505722</v>
       </c>
       <c r="E11">
-        <v>1.593</v>
+        <v>1.77</v>
       </c>
       <c r="F11">
-        <v>1.593</v>
+        <v>1.77</v>
       </c>
       <c r="G11">
         <v>11.1</v>
@@ -2183,28 +2183,28 @@
         <v>4.074</v>
       </c>
       <c r="M11">
-        <v>0.08012789999999999</v>
+        <v>0.08903099999999999</v>
       </c>
       <c r="N11">
-        <v>3.9938721</v>
+        <v>3.984969</v>
       </c>
       <c r="O11">
-        <v>0.6390195360000001</v>
+        <v>0.63759504</v>
       </c>
       <c r="P11">
-        <v>3.354852564</v>
+        <v>3.34737396</v>
       </c>
       <c r="Q11">
-        <v>3.500852564</v>
+        <v>3.49337396</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.0854883407570689</v>
+        <v>0.08586417731726841</v>
       </c>
       <c r="T11">
-        <v>0.5463249494102737</v>
+        <v>0.5514984811281739</v>
       </c>
       <c r="U11">
         <v>0.0503</v>
@@ -2221,7 +2221,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>50.84371361286144</v>
+        <v>45.7593422515753</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2229,22 +2229,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.08150295958554156</v>
+        <v>0.08140884908215044</v>
       </c>
       <c r="C12">
-        <v>15.94639275550572</v>
+        <v>15.77103651087619</v>
       </c>
       <c r="D12">
-        <v>6.616392755505722</v>
+        <v>6.618036510876188</v>
       </c>
       <c r="E12">
-        <v>1.77</v>
+        <v>1.947</v>
       </c>
       <c r="F12">
-        <v>1.77</v>
+        <v>1.947</v>
       </c>
       <c r="G12">
         <v>11.1</v>
@@ -2265,28 +2265,28 @@
         <v>4.074</v>
       </c>
       <c r="M12">
-        <v>0.089031</v>
+        <v>0.09793409999999998</v>
       </c>
       <c r="N12">
-        <v>3.984969</v>
+        <v>3.9760659</v>
       </c>
       <c r="O12">
-        <v>0.63759504</v>
+        <v>0.6361705440000001</v>
       </c>
       <c r="P12">
-        <v>3.34737396</v>
+        <v>3.339895356</v>
       </c>
       <c r="Q12">
-        <v>3.49337396</v>
+        <v>3.485895356</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.08586417731726841</v>
+        <v>0.08624845964286568</v>
       </c>
       <c r="T12">
-        <v>0.5514984811281739</v>
+        <v>0.5567882719858024</v>
       </c>
       <c r="U12">
         <v>0.0503</v>
@@ -2303,7 +2303,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>45.7593422515753</v>
+        <v>41.59940204688664</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2311,22 +2311,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.08140884908215044</v>
+        <v>0.08131473857875933</v>
       </c>
       <c r="C13">
-        <v>15.77103651087619</v>
+        <v>15.59568108318823</v>
       </c>
       <c r="D13">
-        <v>6.618036510876188</v>
+        <v>6.619681083188223</v>
       </c>
       <c r="E13">
-        <v>1.947</v>
+        <v>2.124</v>
       </c>
       <c r="F13">
-        <v>1.947</v>
+        <v>2.124</v>
       </c>
       <c r="G13">
         <v>11.1</v>
@@ -2347,28 +2347,28 @@
         <v>4.074</v>
       </c>
       <c r="M13">
-        <v>0.09793409999999998</v>
+        <v>0.1068372</v>
       </c>
       <c r="N13">
-        <v>3.9760659</v>
+        <v>3.9671628</v>
       </c>
       <c r="O13">
-        <v>0.6361705440000001</v>
+        <v>0.634746048</v>
       </c>
       <c r="P13">
-        <v>3.339895356</v>
+        <v>3.332416751999999</v>
       </c>
       <c r="Q13">
-        <v>3.485895356</v>
+        <v>3.478416751999999</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.08624845964286568</v>
+        <v>0.08664147565768104</v>
       </c>
       <c r="T13">
-        <v>0.5567882719858024</v>
+        <v>0.5621982853629224</v>
       </c>
       <c r="U13">
         <v>0.0503</v>
@@ -2385,7 +2385,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>41.59940204688664</v>
+        <v>38.13278520964608</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2393,22 +2393,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.08131473857875933</v>
+        <v>0.0812206280753682</v>
       </c>
       <c r="C14">
-        <v>15.59568108318823</v>
+        <v>15.42032647305101</v>
       </c>
       <c r="D14">
-        <v>6.619681083188223</v>
+        <v>6.621326473051007</v>
       </c>
       <c r="E14">
-        <v>2.124</v>
+        <v>2.301</v>
       </c>
       <c r="F14">
-        <v>2.124</v>
+        <v>2.301</v>
       </c>
       <c r="G14">
         <v>11.1</v>
@@ -2429,28 +2429,28 @@
         <v>4.074</v>
       </c>
       <c r="M14">
-        <v>0.1068372</v>
+        <v>0.1157403</v>
       </c>
       <c r="N14">
-        <v>3.9671628</v>
+        <v>3.9582597</v>
       </c>
       <c r="O14">
-        <v>0.634746048</v>
+        <v>0.633321552</v>
       </c>
       <c r="P14">
-        <v>3.332416751999999</v>
+        <v>3.324938148</v>
       </c>
       <c r="Q14">
-        <v>3.478416751999999</v>
+        <v>3.470938148</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.08664147565768104</v>
+        <v>0.08704352652341173</v>
       </c>
       <c r="T14">
-        <v>0.5621982853629224</v>
+        <v>0.5677326668636543</v>
       </c>
       <c r="U14">
         <v>0.0503</v>
@@ -2467,7 +2467,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>38.13278520964608</v>
+        <v>35.1994940396733</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2475,22 +2475,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.0812206280753682</v>
+        <v>0.08112651757197707</v>
       </c>
       <c r="C15">
-        <v>15.42032647305101</v>
+        <v>15.24497268107432</v>
       </c>
       <c r="D15">
-        <v>6.621326473051007</v>
+        <v>6.622972681074324</v>
       </c>
       <c r="E15">
-        <v>2.301</v>
+        <v>2.478</v>
       </c>
       <c r="F15">
-        <v>2.301</v>
+        <v>2.478</v>
       </c>
       <c r="G15">
         <v>11.1</v>
@@ -2511,28 +2511,28 @@
         <v>4.074</v>
       </c>
       <c r="M15">
-        <v>0.1157403</v>
+        <v>0.1246434</v>
       </c>
       <c r="N15">
-        <v>3.9582597</v>
+        <v>3.9493566</v>
       </c>
       <c r="O15">
-        <v>0.633321552</v>
+        <v>0.631897056</v>
       </c>
       <c r="P15">
-        <v>3.324938148</v>
+        <v>3.317459544</v>
       </c>
       <c r="Q15">
-        <v>3.470938148</v>
+        <v>3.463459544</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.08704352652341173</v>
+        <v>0.08745492740927567</v>
       </c>
       <c r="T15">
-        <v>0.5677326668636543</v>
+        <v>0.5733957549109149</v>
       </c>
       <c r="U15">
         <v>0.0503</v>
@@ -2549,7 +2549,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>35.1994940396733</v>
+        <v>32.68524446541092</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2557,22 +2557,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.08112651757197707</v>
+        <v>0.08103240706858594</v>
       </c>
       <c r="C16">
-        <v>15.24497268107432</v>
+        <v>15.06961970786856</v>
       </c>
       <c r="D16">
-        <v>6.622972681074324</v>
+        <v>6.624619707868562</v>
       </c>
       <c r="E16">
-        <v>2.478</v>
+        <v>2.655</v>
       </c>
       <c r="F16">
-        <v>2.478</v>
+        <v>2.655</v>
       </c>
       <c r="G16">
         <v>11.1</v>
@@ -2593,28 +2593,28 @@
         <v>4.074</v>
       </c>
       <c r="M16">
-        <v>0.1246434</v>
+        <v>0.1335465</v>
       </c>
       <c r="N16">
-        <v>3.9493566</v>
+        <v>3.9404535</v>
       </c>
       <c r="O16">
-        <v>0.631897056</v>
+        <v>0.63047256</v>
       </c>
       <c r="P16">
-        <v>3.317459544</v>
+        <v>3.30998094</v>
       </c>
       <c r="Q16">
-        <v>3.463459544</v>
+        <v>3.45598094</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.08745492740927567</v>
+        <v>0.08787600831598347</v>
       </c>
       <c r="T16">
-        <v>0.5733957549109149</v>
+        <v>0.5791920920886992</v>
       </c>
       <c r="U16">
         <v>0.0503</v>
@@ -2631,7 +2631,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>32.68524446541092</v>
+        <v>30.50622816771686</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2639,22 +2639,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.08103240706858594</v>
+        <v>0.08093829656519483</v>
       </c>
       <c r="C17">
-        <v>15.06961970786856</v>
+        <v>14.89426755404472</v>
       </c>
       <c r="D17">
-        <v>6.624619707868562</v>
+        <v>6.626267554044718</v>
       </c>
       <c r="E17">
-        <v>2.655</v>
+        <v>2.832</v>
       </c>
       <c r="F17">
-        <v>2.655</v>
+        <v>2.832</v>
       </c>
       <c r="G17">
         <v>11.1</v>
@@ -2675,28 +2675,28 @@
         <v>4.074</v>
       </c>
       <c r="M17">
-        <v>0.1335465</v>
+        <v>0.1424496</v>
       </c>
       <c r="N17">
-        <v>3.9404535</v>
+        <v>3.9315504</v>
       </c>
       <c r="O17">
-        <v>0.63047256</v>
+        <v>0.629048064</v>
       </c>
       <c r="P17">
-        <v>3.30998094</v>
+        <v>3.302502336</v>
       </c>
       <c r="Q17">
-        <v>3.45598094</v>
+        <v>3.448502336</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.08787600831598347</v>
+        <v>0.08830711495856527</v>
       </c>
       <c r="T17">
-        <v>0.5791920920886992</v>
+        <v>0.5851264372945261</v>
       </c>
       <c r="U17">
         <v>0.0503</v>
@@ -2713,7 +2713,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>30.50622816771687</v>
+        <v>28.59958890723456</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2721,22 +2721,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.08093829656519483</v>
+        <v>0.0808441860618037</v>
       </c>
       <c r="C18">
-        <v>14.89426755404472</v>
+        <v>14.7189162202144</v>
       </c>
       <c r="D18">
-        <v>6.626267554044718</v>
+        <v>6.627916220214399</v>
       </c>
       <c r="E18">
-        <v>2.832</v>
+        <v>3.009</v>
       </c>
       <c r="F18">
-        <v>2.832</v>
+        <v>3.009</v>
       </c>
       <c r="G18">
         <v>11.1</v>
@@ -2757,28 +2757,28 @@
         <v>4.074</v>
       </c>
       <c r="M18">
-        <v>0.1424496</v>
+        <v>0.1513527</v>
       </c>
       <c r="N18">
-        <v>3.9315504</v>
+        <v>3.9226473</v>
       </c>
       <c r="O18">
-        <v>0.629048064</v>
+        <v>0.627623568</v>
       </c>
       <c r="P18">
-        <v>3.302502336</v>
+        <v>3.295023732</v>
       </c>
       <c r="Q18">
-        <v>3.448502336</v>
+        <v>3.441023732</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.08830711495856527</v>
+        <v>0.08874860971301651</v>
       </c>
       <c r="T18">
-        <v>0.5851264372945261</v>
+        <v>0.5912037787703729</v>
       </c>
       <c r="U18">
         <v>0.0503</v>
@@ -2795,7 +2795,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>28.59958890723456</v>
+        <v>26.91726014798547</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2803,22 +2803,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.0808441860618037</v>
+        <v>0.08075007555841258</v>
       </c>
       <c r="C19">
-        <v>14.7189162202144</v>
+        <v>14.54356570698982</v>
       </c>
       <c r="D19">
-        <v>6.627916220214399</v>
+        <v>6.629565706989819</v>
       </c>
       <c r="E19">
-        <v>3.009</v>
+        <v>3.186</v>
       </c>
       <c r="F19">
-        <v>3.009</v>
+        <v>3.186</v>
       </c>
       <c r="G19">
         <v>11.1</v>
@@ -2839,28 +2839,28 @@
         <v>4.074</v>
       </c>
       <c r="M19">
-        <v>0.1513527</v>
+        <v>0.1602558</v>
       </c>
       <c r="N19">
-        <v>3.9226473</v>
+        <v>3.9137442</v>
       </c>
       <c r="O19">
-        <v>0.627623568</v>
+        <v>0.626199072</v>
       </c>
       <c r="P19">
-        <v>3.295023732</v>
+        <v>3.287545128</v>
       </c>
       <c r="Q19">
-        <v>3.441023732</v>
+        <v>3.433545128</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.08874860971301651</v>
+        <v>0.08920087263221047</v>
       </c>
       <c r="T19">
-        <v>0.5912037787703729</v>
+        <v>0.5974293480870939</v>
       </c>
       <c r="U19">
         <v>0.0503</v>
@@ -2877,7 +2877,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>26.91726014798547</v>
+        <v>25.42185680643072</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2885,22 +2885,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.0807500755584126</v>
+        <v>0.08065596505502146</v>
       </c>
       <c r="C20">
-        <v>14.54356570698982</v>
+        <v>14.3682160149838</v>
       </c>
       <c r="D20">
-        <v>6.629565706989819</v>
+        <v>6.631216014983803</v>
       </c>
       <c r="E20">
-        <v>3.186</v>
+        <v>3.363</v>
       </c>
       <c r="F20">
-        <v>3.186</v>
+        <v>3.363</v>
       </c>
       <c r="G20">
         <v>11.1</v>
@@ -2921,28 +2921,28 @@
         <v>4.074</v>
       </c>
       <c r="M20">
-        <v>0.1602558</v>
+        <v>0.1691589</v>
       </c>
       <c r="N20">
-        <v>3.9137442</v>
+        <v>3.9048411</v>
       </c>
       <c r="O20">
-        <v>0.626199072</v>
+        <v>0.624774576</v>
       </c>
       <c r="P20">
-        <v>3.287545128</v>
+        <v>3.280066524</v>
       </c>
       <c r="Q20">
-        <v>3.433545128</v>
+        <v>3.426066523999999</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.08920087263221047</v>
+        <v>0.08966430253706352</v>
       </c>
       <c r="T20">
-        <v>0.5974293480870939</v>
+        <v>0.6038086351647216</v>
       </c>
       <c r="U20">
         <v>0.0503</v>
@@ -2959,7 +2959,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>25.42185680643072</v>
+        <v>24.08386434293436</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2967,22 +2967,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.08065596505502146</v>
+        <v>0.08056185455163033</v>
       </c>
       <c r="C21">
-        <v>14.3682160149838</v>
+        <v>14.19286714480978</v>
       </c>
       <c r="D21">
-        <v>6.631216014983803</v>
+        <v>6.632867144809783</v>
       </c>
       <c r="E21">
-        <v>3.363</v>
+        <v>3.54</v>
       </c>
       <c r="F21">
-        <v>3.363</v>
+        <v>3.54</v>
       </c>
       <c r="G21">
         <v>11.1</v>
@@ -3003,28 +3003,28 @@
         <v>4.074</v>
       </c>
       <c r="M21">
-        <v>0.1691589</v>
+        <v>0.178062</v>
       </c>
       <c r="N21">
-        <v>3.9048411</v>
+        <v>3.895938</v>
       </c>
       <c r="O21">
-        <v>0.624774576</v>
+        <v>0.6233500799999999</v>
       </c>
       <c r="P21">
-        <v>3.280066524</v>
+        <v>3.27258792</v>
       </c>
       <c r="Q21">
-        <v>3.426066523999999</v>
+        <v>3.41858792</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.08966430253706352</v>
+        <v>0.09013931818953791</v>
       </c>
       <c r="T21">
-        <v>0.6038086351647216</v>
+        <v>0.6103474044192901</v>
       </c>
       <c r="U21">
         <v>0.0503</v>
@@ -3041,7 +3041,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>24.08386434293436</v>
+        <v>22.87967112578765</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3049,22 +3049,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.08056185455163033</v>
+        <v>0.08046774404823921</v>
       </c>
       <c r="C22">
-        <v>14.19286714480978</v>
+        <v>14.01751909708181</v>
       </c>
       <c r="D22">
-        <v>6.632867144809783</v>
+        <v>6.634519097081807</v>
       </c>
       <c r="E22">
-        <v>3.54</v>
+        <v>3.717</v>
       </c>
       <c r="F22">
-        <v>3.54</v>
+        <v>3.717</v>
       </c>
       <c r="G22">
         <v>11.1</v>
@@ -3085,28 +3085,28 @@
         <v>4.074</v>
       </c>
       <c r="M22">
-        <v>0.178062</v>
+        <v>0.1869651</v>
       </c>
       <c r="N22">
-        <v>3.895938</v>
+        <v>3.8870349</v>
       </c>
       <c r="O22">
-        <v>0.6233500799999999</v>
+        <v>0.621925584</v>
       </c>
       <c r="P22">
-        <v>3.27258792</v>
+        <v>3.265109316</v>
       </c>
       <c r="Q22">
-        <v>3.41858792</v>
+        <v>3.411109316</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.09013931818953791</v>
+        <v>0.09062635955473317</v>
       </c>
       <c r="T22">
-        <v>0.6103474044192901</v>
+        <v>0.6170517121359995</v>
       </c>
       <c r="U22">
         <v>0.0503</v>
@@ -3123,7 +3123,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>22.87967112578765</v>
+        <v>21.79016297694061</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3131,22 +3131,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.0804677440482392</v>
+        <v>0.08037363354484808</v>
       </c>
       <c r="C23">
-        <v>14.01751909708181</v>
+        <v>13.84217187241453</v>
       </c>
       <c r="D23">
-        <v>6.634519097081807</v>
+        <v>6.63617187241453</v>
       </c>
       <c r="E23">
-        <v>3.717</v>
+        <v>3.894</v>
       </c>
       <c r="F23">
-        <v>3.717</v>
+        <v>3.894</v>
       </c>
       <c r="G23">
         <v>11.1</v>
@@ -3167,28 +3167,28 @@
         <v>4.074</v>
       </c>
       <c r="M23">
-        <v>0.1869651</v>
+        <v>0.1958682</v>
       </c>
       <c r="N23">
-        <v>3.8870349</v>
+        <v>3.8781318</v>
       </c>
       <c r="O23">
-        <v>0.621925584</v>
+        <v>0.620501088</v>
       </c>
       <c r="P23">
-        <v>3.265109316</v>
+        <v>3.257630712</v>
       </c>
       <c r="Q23">
-        <v>3.411109316</v>
+        <v>3.403630712</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.09062635955473317</v>
+        <v>0.09112588916006163</v>
       </c>
       <c r="T23">
-        <v>0.6170517121359995</v>
+        <v>0.6239279251787784</v>
       </c>
       <c r="U23">
         <v>0.0503</v>
@@ -3205,7 +3205,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>21.79016297694062</v>
+        <v>20.79970102344332</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3213,22 +3213,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.08037363354484808</v>
+        <v>0.08027952304145695</v>
       </c>
       <c r="C24">
-        <v>13.84217187241453</v>
+        <v>13.66682547142322</v>
       </c>
       <c r="D24">
-        <v>6.63617187241453</v>
+        <v>6.637825471423222</v>
       </c>
       <c r="E24">
-        <v>3.894</v>
+        <v>4.071</v>
       </c>
       <c r="F24">
-        <v>3.894</v>
+        <v>4.071</v>
       </c>
       <c r="G24">
         <v>11.1</v>
@@ -3249,28 +3249,28 @@
         <v>4.074</v>
       </c>
       <c r="M24">
-        <v>0.1958682</v>
+        <v>0.2047713</v>
       </c>
       <c r="N24">
-        <v>3.8781318</v>
+        <v>3.8692287</v>
       </c>
       <c r="O24">
-        <v>0.620501088</v>
+        <v>0.619076592</v>
       </c>
       <c r="P24">
-        <v>3.257630712</v>
+        <v>3.250152108</v>
       </c>
       <c r="Q24">
-        <v>3.403630712</v>
+        <v>3.396152108</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.09112588916006163</v>
+        <v>0.09163839356033371</v>
       </c>
       <c r="T24">
-        <v>0.6239279251787784</v>
+        <v>0.6309827411577335</v>
       </c>
       <c r="U24">
         <v>0.0503</v>
@@ -3287,7 +3287,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>20.79970102344332</v>
+        <v>19.89536619633709</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3295,22 +3295,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.08027952304145695</v>
+        <v>0.08018541253806583</v>
       </c>
       <c r="C25">
-        <v>13.66682547142322</v>
+        <v>13.49147989472377</v>
       </c>
       <c r="D25">
-        <v>6.637825471423222</v>
+        <v>6.639479894723769</v>
       </c>
       <c r="E25">
-        <v>4.071</v>
+        <v>4.248</v>
       </c>
       <c r="F25">
-        <v>4.071</v>
+        <v>4.248</v>
       </c>
       <c r="G25">
         <v>11.1</v>
@@ -3331,28 +3331,28 @@
         <v>4.074</v>
       </c>
       <c r="M25">
-        <v>0.2047713</v>
+        <v>0.2136744</v>
       </c>
       <c r="N25">
-        <v>3.8692287</v>
+        <v>3.8603256</v>
       </c>
       <c r="O25">
-        <v>0.619076592</v>
+        <v>0.617652096</v>
       </c>
       <c r="P25">
-        <v>3.250152108</v>
+        <v>3.242673504</v>
       </c>
       <c r="Q25">
-        <v>3.396152108</v>
+        <v>3.388673504</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.09163839356033371</v>
+        <v>0.09216438491850767</v>
       </c>
       <c r="T25">
-        <v>0.6309827411577335</v>
+        <v>0.6382232101887662</v>
       </c>
       <c r="U25">
         <v>0.0503</v>
@@ -3369,7 +3369,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>19.89536619633709</v>
+        <v>19.06639260482304</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3377,22 +3377,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.08018541253806583</v>
+        <v>0.08009130203467471</v>
       </c>
       <c r="C26">
-        <v>13.49147989472377</v>
+        <v>13.31613514293266</v>
       </c>
       <c r="D26">
-        <v>6.639479894723769</v>
+        <v>6.641135142932665</v>
       </c>
       <c r="E26">
-        <v>4.247999999999999</v>
+        <v>4.425</v>
       </c>
       <c r="F26">
-        <v>4.247999999999999</v>
+        <v>4.425</v>
       </c>
       <c r="G26">
         <v>11.1</v>
@@ -3413,28 +3413,28 @@
         <v>4.074</v>
       </c>
       <c r="M26">
-        <v>0.2136744</v>
+        <v>0.2225775</v>
       </c>
       <c r="N26">
-        <v>3.8603256</v>
+        <v>3.8514225</v>
       </c>
       <c r="O26">
-        <v>0.617652096</v>
+        <v>0.6162276</v>
       </c>
       <c r="P26">
-        <v>3.242673504</v>
+        <v>3.2351949</v>
       </c>
       <c r="Q26">
-        <v>3.388673504</v>
+        <v>3.3811949</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.09216438491850767</v>
+        <v>0.09270440271289961</v>
       </c>
       <c r="T26">
-        <v>0.6382232101887662</v>
+        <v>0.6456567583939598</v>
       </c>
       <c r="U26">
         <v>0.0503</v>
@@ -3451,7 +3451,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>19.06639260482304</v>
+        <v>18.30373690063012</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3459,22 +3459,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.08009130203467471</v>
+        <v>0.07999719153128358</v>
       </c>
       <c r="C27">
-        <v>13.31613514293266</v>
+        <v>13.14079121666703</v>
       </c>
       <c r="D27">
-        <v>6.641135142932665</v>
+        <v>6.642791216667027</v>
       </c>
       <c r="E27">
-        <v>4.425</v>
+        <v>4.602</v>
       </c>
       <c r="F27">
-        <v>4.425</v>
+        <v>4.602</v>
       </c>
       <c r="G27">
         <v>11.1</v>
@@ -3495,28 +3495,28 @@
         <v>4.074</v>
       </c>
       <c r="M27">
-        <v>0.2225775</v>
+        <v>0.2314806</v>
       </c>
       <c r="N27">
-        <v>3.8514225</v>
+        <v>3.8425194</v>
       </c>
       <c r="O27">
-        <v>0.6162276</v>
+        <v>0.614803104</v>
       </c>
       <c r="P27">
-        <v>3.2351949</v>
+        <v>3.227716296</v>
       </c>
       <c r="Q27">
-        <v>3.3811949</v>
+        <v>3.373716296</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.09270440271289961</v>
+        <v>0.09325901558281566</v>
       </c>
       <c r="T27">
-        <v>0.6456567583939598</v>
+        <v>0.6532912133074019</v>
       </c>
       <c r="U27">
         <v>0.0503</v>
@@ -3533,7 +3533,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>18.30373690063012</v>
+        <v>17.59974701983665</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3541,22 +3541,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.07999719153128358</v>
+        <v>0.07990308102789245</v>
       </c>
       <c r="C28">
-        <v>13.14079121666703</v>
+        <v>12.96544811654458</v>
       </c>
       <c r="D28">
-        <v>6.642791216667027</v>
+        <v>6.644448116544577</v>
       </c>
       <c r="E28">
-        <v>4.602</v>
+        <v>4.779</v>
       </c>
       <c r="F28">
-        <v>4.602</v>
+        <v>4.779</v>
       </c>
       <c r="G28">
         <v>11.1</v>
@@ -3577,28 +3577,28 @@
         <v>4.074</v>
       </c>
       <c r="M28">
-        <v>0.2314806</v>
+        <v>0.2403837</v>
       </c>
       <c r="N28">
-        <v>3.8425194</v>
+        <v>3.8336163</v>
       </c>
       <c r="O28">
-        <v>0.614803104</v>
+        <v>0.613378608</v>
       </c>
       <c r="P28">
-        <v>3.227716296</v>
+        <v>3.220237692</v>
       </c>
       <c r="Q28">
-        <v>3.373716296</v>
+        <v>3.366237692</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.09325901558281566</v>
+        <v>0.09382882332588008</v>
       </c>
       <c r="T28">
-        <v>0.6532912133074019</v>
+        <v>0.6611348313691575</v>
       </c>
       <c r="U28">
         <v>0.0503</v>
@@ -3615,7 +3615,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>17.59974701983665</v>
+        <v>16.94790453762048</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3623,22 +3623,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.07990308102789245</v>
+        <v>0.07980897052450132</v>
       </c>
       <c r="C29">
-        <v>12.96544811654458</v>
+        <v>12.79010584318366</v>
       </c>
       <c r="D29">
-        <v>6.644448116544577</v>
+        <v>6.646105843183665</v>
       </c>
       <c r="E29">
-        <v>4.779</v>
+        <v>4.956</v>
       </c>
       <c r="F29">
-        <v>4.779</v>
+        <v>4.956</v>
       </c>
       <c r="G29">
         <v>11.1</v>
@@ -3659,28 +3659,28 @@
         <v>4.074</v>
       </c>
       <c r="M29">
-        <v>0.2403837</v>
+        <v>0.2492868</v>
       </c>
       <c r="N29">
-        <v>3.8336163</v>
+        <v>3.8247132</v>
       </c>
       <c r="O29">
-        <v>0.613378608</v>
+        <v>0.6119541119999999</v>
       </c>
       <c r="P29">
-        <v>3.220237692</v>
+        <v>3.212759088</v>
       </c>
       <c r="Q29">
-        <v>3.366237692</v>
+        <v>3.358759088</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.09382882332588008</v>
+        <v>0.0944144590618074</v>
       </c>
       <c r="T29">
-        <v>0.6611348313691575</v>
+        <v>0.6691963277104063</v>
       </c>
       <c r="U29">
         <v>0.0503</v>
@@ -3697,7 +3697,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>16.94790453762048</v>
+        <v>16.34262223270546</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3705,22 +3705,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.07980897052450132</v>
+        <v>0.07971486002111021</v>
       </c>
       <c r="C30">
-        <v>12.79010584318366</v>
+        <v>12.61476439720325</v>
       </c>
       <c r="D30">
-        <v>6.646105843183665</v>
+        <v>6.647764397203251</v>
       </c>
       <c r="E30">
-        <v>4.956</v>
+        <v>5.133</v>
       </c>
       <c r="F30">
-        <v>4.956</v>
+        <v>5.133</v>
       </c>
       <c r="G30">
         <v>11.1</v>
@@ -3741,28 +3741,28 @@
         <v>4.074</v>
       </c>
       <c r="M30">
-        <v>0.2492868</v>
+        <v>0.2581899</v>
       </c>
       <c r="N30">
-        <v>3.8247132</v>
+        <v>3.8158101</v>
       </c>
       <c r="O30">
-        <v>0.6119541119999999</v>
+        <v>0.610529616</v>
       </c>
       <c r="P30">
-        <v>3.212759088</v>
+        <v>3.205280484</v>
       </c>
       <c r="Q30">
-        <v>3.358759088</v>
+        <v>3.351280484</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.0944144590618074</v>
+        <v>0.09501659157902848</v>
       </c>
       <c r="T30">
-        <v>0.6691963277104063</v>
+        <v>0.6774849084556339</v>
       </c>
       <c r="U30">
         <v>0.0503</v>
@@ -3779,7 +3779,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>16.34262223270546</v>
+        <v>15.77908353502596</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3787,22 +3787,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.0797148600211102</v>
+        <v>0.07962074951771908</v>
       </c>
       <c r="C31">
-        <v>12.61476439720325</v>
+        <v>12.43942377922292</v>
       </c>
       <c r="D31">
-        <v>6.647764397203251</v>
+        <v>6.649423779222915</v>
       </c>
       <c r="E31">
-        <v>5.132999999999999</v>
+        <v>5.31</v>
       </c>
       <c r="F31">
-        <v>5.132999999999999</v>
+        <v>5.31</v>
       </c>
       <c r="G31">
         <v>11.1</v>
@@ -3823,28 +3823,28 @@
         <v>4.074</v>
       </c>
       <c r="M31">
-        <v>0.2581898999999999</v>
+        <v>0.267093</v>
       </c>
       <c r="N31">
-        <v>3.8158101</v>
+        <v>3.806907</v>
       </c>
       <c r="O31">
-        <v>0.610529616</v>
+        <v>0.6091051199999999</v>
       </c>
       <c r="P31">
-        <v>3.205280484</v>
+        <v>3.19780188</v>
       </c>
       <c r="Q31">
-        <v>3.351280484</v>
+        <v>3.34380188</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.09501659157902845</v>
+        <v>0.09563592788245584</v>
       </c>
       <c r="T31">
-        <v>0.6774849084556338</v>
+        <v>0.6860103057935822</v>
       </c>
       <c r="U31">
         <v>0.0503</v>
@@ -3861,7 +3861,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>15.77908353502597</v>
+        <v>15.25311408385843</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3869,22 +3869,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.07962074951771908</v>
+        <v>0.07952663901432797</v>
       </c>
       <c r="C32">
-        <v>12.43942377922292</v>
+        <v>12.26408398986286</v>
       </c>
       <c r="D32">
-        <v>6.649423779222915</v>
+        <v>6.651083989862855</v>
       </c>
       <c r="E32">
-        <v>5.31</v>
+        <v>5.487</v>
       </c>
       <c r="F32">
-        <v>5.31</v>
+        <v>5.487</v>
       </c>
       <c r="G32">
         <v>11.1</v>
@@ -3905,28 +3905,28 @@
         <v>4.074</v>
       </c>
       <c r="M32">
-        <v>0.267093</v>
+        <v>0.2759961</v>
       </c>
       <c r="N32">
-        <v>3.806907</v>
+        <v>3.7980039</v>
       </c>
       <c r="O32">
-        <v>0.6091051199999999</v>
+        <v>0.607680624</v>
       </c>
       <c r="P32">
-        <v>3.19780188</v>
+        <v>3.190323276</v>
       </c>
       <c r="Q32">
-        <v>3.34380188</v>
+        <v>3.336323276</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.09563592788245584</v>
+        <v>0.09627321596279415</v>
       </c>
       <c r="T32">
-        <v>0.6860103057935822</v>
+        <v>0.6947828160978481</v>
       </c>
       <c r="U32">
         <v>0.0503</v>
@@ -3943,7 +3943,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>15.25311408385843</v>
+        <v>14.76107814566945</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3951,22 +3951,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.07952663901432797</v>
+        <v>0.07943252851093684</v>
       </c>
       <c r="C33">
-        <v>12.26408398986286</v>
+        <v>12.08874502974389</v>
       </c>
       <c r="D33">
-        <v>6.651083989862855</v>
+        <v>6.652745029743889</v>
       </c>
       <c r="E33">
-        <v>5.487</v>
+        <v>5.664</v>
       </c>
       <c r="F33">
-        <v>5.487</v>
+        <v>5.664</v>
       </c>
       <c r="G33">
         <v>11.1</v>
@@ -3987,28 +3987,28 @@
         <v>4.074</v>
       </c>
       <c r="M33">
-        <v>0.2759961</v>
+        <v>0.2848992</v>
       </c>
       <c r="N33">
-        <v>3.7980039</v>
+        <v>3.7891008</v>
       </c>
       <c r="O33">
-        <v>0.607680624</v>
+        <v>0.6062561279999999</v>
       </c>
       <c r="P33">
-        <v>3.190323276</v>
+        <v>3.182844672</v>
       </c>
       <c r="Q33">
-        <v>3.336323276</v>
+        <v>3.328844672</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.09627321596279415</v>
+        <v>0.09692924781020124</v>
       </c>
       <c r="T33">
-        <v>0.6947828160978481</v>
+        <v>0.7038133414110628</v>
       </c>
       <c r="U33">
         <v>0.0503</v>
@@ -4025,7 +4025,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>14.76107814566945</v>
+        <v>14.29979445361728</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4033,22 +4033,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.07943252851093684</v>
+        <v>0.07933841800754569</v>
       </c>
       <c r="C34">
-        <v>12.08874502974389</v>
+        <v>11.91340689948746</v>
       </c>
       <c r="D34">
-        <v>6.652745029743889</v>
+        <v>6.654406899487455</v>
       </c>
       <c r="E34">
-        <v>5.664</v>
+        <v>5.841</v>
       </c>
       <c r="F34">
-        <v>5.664</v>
+        <v>5.841</v>
       </c>
       <c r="G34">
         <v>11.1</v>
@@ -4069,28 +4069,28 @@
         <v>4.074</v>
       </c>
       <c r="M34">
-        <v>0.2848992</v>
+        <v>0.2938023</v>
       </c>
       <c r="N34">
-        <v>3.7891008</v>
+        <v>3.7801977</v>
       </c>
       <c r="O34">
-        <v>0.6062561279999999</v>
+        <v>0.604831632</v>
       </c>
       <c r="P34">
-        <v>3.182844672</v>
+        <v>3.175366068</v>
       </c>
       <c r="Q34">
-        <v>3.328844672</v>
+        <v>3.321366068</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.09692924781020124</v>
+        <v>0.09760486269782942</v>
       </c>
       <c r="T34">
-        <v>0.7038133414110628</v>
+        <v>0.713113434644075</v>
       </c>
       <c r="U34">
         <v>0.0503</v>
@@ -4107,7 +4107,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>14.29979445361728</v>
+        <v>13.86646734896221</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4115,22 +4115,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.07933841800754569</v>
+        <v>0.07924430750415459</v>
       </c>
       <c r="C35">
-        <v>11.91340689948746</v>
+        <v>11.73806959971562</v>
       </c>
       <c r="D35">
-        <v>6.654406899487455</v>
+        <v>6.656069599715616</v>
       </c>
       <c r="E35">
-        <v>5.841</v>
+        <v>6.018</v>
       </c>
       <c r="F35">
-        <v>5.841</v>
+        <v>6.018</v>
       </c>
       <c r="G35">
         <v>11.1</v>
@@ -4151,28 +4151,28 @@
         <v>4.074</v>
       </c>
       <c r="M35">
-        <v>0.2938023</v>
+        <v>0.3027054</v>
       </c>
       <c r="N35">
-        <v>3.7801977</v>
+        <v>3.7712946</v>
       </c>
       <c r="O35">
-        <v>0.604831632</v>
+        <v>0.6034071360000001</v>
       </c>
       <c r="P35">
-        <v>3.175366068</v>
+        <v>3.167887464</v>
       </c>
       <c r="Q35">
-        <v>3.321366068</v>
+        <v>3.313887464</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.09760486269782942</v>
+        <v>0.09830095076387059</v>
       </c>
       <c r="T35">
-        <v>0.713113434644075</v>
+        <v>0.7226953488841482</v>
       </c>
       <c r="U35">
         <v>0.0503</v>
@@ -4189,7 +4189,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>13.86646734896221</v>
+        <v>13.45863007399273</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4197,22 +4197,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.07924430750415459</v>
+        <v>0.07915019700076346</v>
       </c>
       <c r="C36">
-        <v>11.73806959971562</v>
+        <v>11.56273313105105</v>
       </c>
       <c r="D36">
-        <v>6.656069599715616</v>
+        <v>6.657733131051049</v>
       </c>
       <c r="E36">
-        <v>6.018</v>
+        <v>6.195</v>
       </c>
       <c r="F36">
-        <v>6.018</v>
+        <v>6.195</v>
       </c>
       <c r="G36">
         <v>11.1</v>
@@ -4233,28 +4233,28 @@
         <v>4.074</v>
       </c>
       <c r="M36">
-        <v>0.3027054</v>
+        <v>0.3116085</v>
       </c>
       <c r="N36">
-        <v>3.7712946</v>
+        <v>3.7623915</v>
       </c>
       <c r="O36">
-        <v>0.6034071360000001</v>
+        <v>0.60198264</v>
       </c>
       <c r="P36">
-        <v>3.167887464</v>
+        <v>3.16040886</v>
       </c>
       <c r="Q36">
-        <v>3.313887464</v>
+        <v>3.306408859999999</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.09830095076387059</v>
+        <v>0.09901845692425149</v>
       </c>
       <c r="T36">
-        <v>0.7226953488841482</v>
+        <v>0.7325720912546851</v>
       </c>
       <c r="U36">
         <v>0.0503</v>
@@ -4271,7 +4271,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>13.45863007399273</v>
+        <v>13.07409778616437</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4279,22 +4279,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.07915019700076346</v>
+        <v>0.07950968649737232</v>
       </c>
       <c r="C37">
-        <v>11.56273313105105</v>
+        <v>11.37938313864339</v>
       </c>
       <c r="D37">
-        <v>6.657733131051049</v>
+        <v>6.651383138643394</v>
       </c>
       <c r="E37">
-        <v>6.195</v>
+        <v>6.372000000000001</v>
       </c>
       <c r="F37">
-        <v>6.195</v>
+        <v>6.372000000000001</v>
       </c>
       <c r="G37">
         <v>11.1</v>
@@ -4315,45 +4315,45 @@
         <v>4.074</v>
       </c>
       <c r="M37">
-        <v>0.3116085</v>
+        <v>0.3300696</v>
       </c>
       <c r="N37">
-        <v>3.7623915</v>
+        <v>3.7439304</v>
       </c>
       <c r="O37">
-        <v>0.60198264</v>
+        <v>0.599028864</v>
       </c>
       <c r="P37">
-        <v>3.16040886</v>
+        <v>3.144901536</v>
       </c>
       <c r="Q37">
-        <v>3.306408859999999</v>
+        <v>3.290901536</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.09901845692425149</v>
+        <v>0.09975838515214427</v>
       </c>
       <c r="T37">
-        <v>0.7325720912546851</v>
+        <v>0.7427574818243015</v>
       </c>
       <c r="U37">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V37">
         <v>0.16</v>
       </c>
       <c r="W37">
-        <v>0.042252</v>
+        <v>0.043512</v>
       </c>
       <c r="X37" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y37">
-        <v>13.07409778616437</v>
+        <v>12.34285132590217</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4361,22 +4361,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.07950968649737233</v>
+        <v>0.07942817599398122</v>
       </c>
       <c r="C38">
-        <v>11.37938313864339</v>
+        <v>11.20382187125526</v>
       </c>
       <c r="D38">
-        <v>6.651383138643394</v>
+        <v>6.652821871255264</v>
       </c>
       <c r="E38">
-        <v>6.372</v>
+        <v>6.548999999999999</v>
       </c>
       <c r="F38">
-        <v>6.372</v>
+        <v>6.548999999999999</v>
       </c>
       <c r="G38">
         <v>11.1</v>
@@ -4397,28 +4397,28 @@
         <v>4.074</v>
       </c>
       <c r="M38">
-        <v>0.3300696</v>
+        <v>0.3392382</v>
       </c>
       <c r="N38">
-        <v>3.7439304</v>
+        <v>3.7347618</v>
       </c>
       <c r="O38">
-        <v>0.599028864</v>
+        <v>0.597561888</v>
       </c>
       <c r="P38">
-        <v>3.144901536</v>
+        <v>3.137199912</v>
       </c>
       <c r="Q38">
-        <v>3.290901536</v>
+        <v>3.283199912</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.09975838515214427</v>
+        <v>0.1005218031650496</v>
       </c>
       <c r="T38">
-        <v>0.7427574818243013</v>
+        <v>0.7532662181262865</v>
       </c>
       <c r="U38">
         <v>0.0518</v>
@@ -4435,7 +4435,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>12.34285132590217</v>
+        <v>12.00926074952644</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4443,22 +4443,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.07942817599398122</v>
+        <v>0.07934666549059008</v>
       </c>
       <c r="C39">
-        <v>11.20382187125526</v>
+        <v>11.02826122641415</v>
       </c>
       <c r="D39">
-        <v>6.652821871255264</v>
+        <v>6.654261226414153</v>
       </c>
       <c r="E39">
-        <v>6.548999999999999</v>
+        <v>6.726</v>
       </c>
       <c r="F39">
-        <v>6.548999999999999</v>
+        <v>6.726</v>
       </c>
       <c r="G39">
         <v>11.1</v>
@@ -4479,28 +4479,28 @@
         <v>4.074</v>
       </c>
       <c r="M39">
-        <v>0.3392382</v>
+        <v>0.3484068</v>
       </c>
       <c r="N39">
-        <v>3.7347618</v>
+        <v>3.7255932</v>
       </c>
       <c r="O39">
-        <v>0.597561888</v>
+        <v>0.596094912</v>
       </c>
       <c r="P39">
-        <v>3.137199912</v>
+        <v>3.129498288</v>
       </c>
       <c r="Q39">
-        <v>3.283199912</v>
+        <v>3.275498288</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.1005218031650496</v>
+        <v>0.1013098475654679</v>
       </c>
       <c r="T39">
-        <v>0.7532662181262865</v>
+        <v>0.7641139459218838</v>
       </c>
       <c r="U39">
         <v>0.0518</v>
@@ -4517,7 +4517,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>12.00926074952644</v>
+        <v>11.69322757190732</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4525,22 +4525,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.07934666549059008</v>
+        <v>0.07926515498719895</v>
       </c>
       <c r="C40">
-        <v>11.02826122641415</v>
+        <v>10.85270120452422</v>
       </c>
       <c r="D40">
-        <v>6.654261226414153</v>
+        <v>6.655701204524215</v>
       </c>
       <c r="E40">
-        <v>6.726</v>
+        <v>6.903</v>
       </c>
       <c r="F40">
-        <v>6.726</v>
+        <v>6.903</v>
       </c>
       <c r="G40">
         <v>11.1</v>
@@ -4561,28 +4561,28 @@
         <v>4.074</v>
       </c>
       <c r="M40">
-        <v>0.3484068</v>
+        <v>0.3575754</v>
       </c>
       <c r="N40">
-        <v>3.7255932</v>
+        <v>3.7164246</v>
       </c>
       <c r="O40">
-        <v>0.596094912</v>
+        <v>0.594627936</v>
       </c>
       <c r="P40">
-        <v>3.129498288</v>
+        <v>3.121796664</v>
       </c>
       <c r="Q40">
-        <v>3.275498288</v>
+        <v>3.267796664</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.1013098475654679</v>
+        <v>0.1021237294872114</v>
       </c>
       <c r="T40">
-        <v>0.7641139459218838</v>
+        <v>0.7753173369238943</v>
       </c>
       <c r="U40">
         <v>0.0518</v>
@@ -4599,7 +4599,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>11.69322757190732</v>
+        <v>11.3934012239097</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4607,22 +4607,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.07926515498719895</v>
+        <v>0.07918364448380784</v>
       </c>
       <c r="C41">
-        <v>10.85270120452422</v>
+        <v>10.67714180598996</v>
       </c>
       <c r="D41">
-        <v>6.655701204524215</v>
+        <v>6.657141805989958</v>
       </c>
       <c r="E41">
-        <v>6.903</v>
+        <v>7.08</v>
       </c>
       <c r="F41">
-        <v>6.903</v>
+        <v>7.08</v>
       </c>
       <c r="G41">
         <v>11.1</v>
@@ -4643,28 +4643,28 @@
         <v>4.074</v>
       </c>
       <c r="M41">
-        <v>0.3575754</v>
+        <v>0.366744</v>
       </c>
       <c r="N41">
-        <v>3.7164246</v>
+        <v>3.707256</v>
       </c>
       <c r="O41">
-        <v>0.594627936</v>
+        <v>0.59316096</v>
       </c>
       <c r="P41">
-        <v>3.121796664</v>
+        <v>3.11409504</v>
       </c>
       <c r="Q41">
-        <v>3.267796664</v>
+        <v>3.260095039999999</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.1021237294872114</v>
+        <v>0.1029647408063464</v>
       </c>
       <c r="T41">
-        <v>0.7753173369238943</v>
+        <v>0.7868941742926385</v>
       </c>
       <c r="U41">
         <v>0.0518</v>
@@ -4681,7 +4681,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>11.3934012239097</v>
+        <v>11.10856619331195</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4689,22 +4689,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.07918364448380784</v>
+        <v>0.07910213398041671</v>
       </c>
       <c r="C42">
-        <v>10.67714180598996</v>
+        <v>10.50158303121624</v>
       </c>
       <c r="D42">
-        <v>6.657141805989958</v>
+        <v>6.658583031216237</v>
       </c>
       <c r="E42">
-        <v>7.08</v>
+        <v>7.257000000000001</v>
       </c>
       <c r="F42">
-        <v>7.08</v>
+        <v>7.257000000000001</v>
       </c>
       <c r="G42">
         <v>11.1</v>
@@ -4725,28 +4725,28 @@
         <v>4.074</v>
       </c>
       <c r="M42">
-        <v>0.366744</v>
+        <v>0.3759126</v>
       </c>
       <c r="N42">
-        <v>3.707256</v>
+        <v>3.6980874</v>
       </c>
       <c r="O42">
-        <v>0.59316096</v>
+        <v>0.591693984</v>
       </c>
       <c r="P42">
-        <v>3.11409504</v>
+        <v>3.106393416</v>
       </c>
       <c r="Q42">
-        <v>3.260095039999999</v>
+        <v>3.252393416</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.1029647408063464</v>
+        <v>0.1038342609837571</v>
       </c>
       <c r="T42">
-        <v>0.7868941742926385</v>
+        <v>0.7988634468264247</v>
       </c>
       <c r="U42">
         <v>0.0518</v>
@@ -4763,7 +4763,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>11.10856619331195</v>
+        <v>10.83762555445069</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4771,22 +4771,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.07910213398041671</v>
+        <v>0.07902062347702558</v>
       </c>
       <c r="C43">
-        <v>10.50158303121624</v>
+        <v>10.32602488060826</v>
       </c>
       <c r="D43">
-        <v>6.658583031216237</v>
+        <v>6.660024880608262</v>
       </c>
       <c r="E43">
-        <v>7.257000000000001</v>
+        <v>7.434</v>
       </c>
       <c r="F43">
-        <v>7.257000000000001</v>
+        <v>7.434</v>
       </c>
       <c r="G43">
         <v>11.1</v>
@@ -4807,28 +4807,28 @@
         <v>4.074</v>
       </c>
       <c r="M43">
-        <v>0.3759126</v>
+        <v>0.3850812</v>
       </c>
       <c r="N43">
-        <v>3.6980874</v>
+        <v>3.6889188</v>
       </c>
       <c r="O43">
-        <v>0.591693984</v>
+        <v>0.5902270079999999</v>
       </c>
       <c r="P43">
-        <v>3.106393416</v>
+        <v>3.098691792</v>
       </c>
       <c r="Q43">
-        <v>3.252393416</v>
+        <v>3.244691792</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.1038342609837571</v>
+        <v>0.1047337646155614</v>
       </c>
       <c r="T43">
-        <v>0.7988634468264247</v>
+        <v>0.8112454528958589</v>
       </c>
       <c r="U43">
         <v>0.0518</v>
@@ -4845,7 +4845,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>10.83762555445069</v>
+        <v>10.57958685077329</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4853,22 +4853,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.0790206234770256</v>
+        <v>0.07893911297363446</v>
       </c>
       <c r="C44">
-        <v>10.32602488060826</v>
+        <v>10.15046735457159</v>
       </c>
       <c r="D44">
-        <v>6.660024880608262</v>
+        <v>6.661467354571587</v>
       </c>
       <c r="E44">
-        <v>7.433999999999999</v>
+        <v>7.611</v>
       </c>
       <c r="F44">
-        <v>7.433999999999999</v>
+        <v>7.611</v>
       </c>
       <c r="G44">
         <v>11.1</v>
@@ -4889,28 +4889,28 @@
         <v>4.074</v>
       </c>
       <c r="M44">
-        <v>0.3850812</v>
+        <v>0.3942498</v>
       </c>
       <c r="N44">
-        <v>3.6889188</v>
+        <v>3.6797502</v>
       </c>
       <c r="O44">
-        <v>0.5902270079999999</v>
+        <v>0.588760032</v>
       </c>
       <c r="P44">
-        <v>3.098691792</v>
+        <v>3.090990168</v>
       </c>
       <c r="Q44">
-        <v>3.244691792</v>
+        <v>3.236990168</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.1047337646155614</v>
+        <v>0.1056648297783061</v>
       </c>
       <c r="T44">
-        <v>0.8112454528958589</v>
+        <v>0.8240619153186065</v>
       </c>
       <c r="U44">
         <v>0.0518</v>
@@ -4927,7 +4927,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>10.57958685077329</v>
+        <v>10.33354994726694</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4935,22 +4935,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.07893911297363446</v>
+        <v>0.07885760247024334</v>
       </c>
       <c r="C45">
-        <v>10.15046735457159</v>
+        <v>9.974910453512123</v>
       </c>
       <c r="D45">
-        <v>6.661467354571587</v>
+        <v>6.662910453512125</v>
       </c>
       <c r="E45">
-        <v>7.611</v>
+        <v>7.787999999999999</v>
       </c>
       <c r="F45">
-        <v>7.611</v>
+        <v>7.787999999999999</v>
       </c>
       <c r="G45">
         <v>11.1</v>
@@ -4971,28 +4971,28 @@
         <v>4.074</v>
       </c>
       <c r="M45">
-        <v>0.3942498</v>
+        <v>0.4034184</v>
       </c>
       <c r="N45">
-        <v>3.6797502</v>
+        <v>3.6705816</v>
       </c>
       <c r="O45">
-        <v>0.588760032</v>
+        <v>0.5872930559999999</v>
       </c>
       <c r="P45">
-        <v>3.090990168</v>
+        <v>3.083288544</v>
       </c>
       <c r="Q45">
-        <v>3.236990168</v>
+        <v>3.229288544</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.1056648297783061</v>
+        <v>0.1066291472682917</v>
       </c>
       <c r="T45">
-        <v>0.8240619153186065</v>
+        <v>0.8373361085421666</v>
       </c>
       <c r="U45">
         <v>0.0518</v>
@@ -5009,7 +5009,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>10.33354994726694</v>
+        <v>10.09869653937451</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5017,22 +5017,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.07885760247024334</v>
+        <v>0.07877609196685222</v>
       </c>
       <c r="C46">
-        <v>9.974910453512123</v>
+        <v>9.79935417783614</v>
       </c>
       <c r="D46">
-        <v>6.662910453512125</v>
+        <v>6.664354177836138</v>
       </c>
       <c r="E46">
-        <v>7.787999999999999</v>
+        <v>7.965</v>
       </c>
       <c r="F46">
-        <v>7.787999999999999</v>
+        <v>7.965</v>
       </c>
       <c r="G46">
         <v>11.1</v>
@@ -5053,28 +5053,28 @@
         <v>4.074</v>
       </c>
       <c r="M46">
-        <v>0.4034184</v>
+        <v>0.412587</v>
       </c>
       <c r="N46">
-        <v>3.6705816</v>
+        <v>3.661413</v>
       </c>
       <c r="O46">
-        <v>0.5872930559999999</v>
+        <v>0.58582608</v>
       </c>
       <c r="P46">
-        <v>3.083288544</v>
+        <v>3.07558692</v>
       </c>
       <c r="Q46">
-        <v>3.229288544</v>
+        <v>3.22158692</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.1066291472682917</v>
+        <v>0.1076285308488222</v>
       </c>
       <c r="T46">
-        <v>0.8373361085421666</v>
+        <v>0.8510929997011287</v>
       </c>
       <c r="U46">
         <v>0.0518</v>
@@ -5091,7 +5091,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>10.09869653937451</v>
+        <v>9.874281060721739</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5099,22 +5099,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.07877609196685222</v>
+        <v>0.07935146146346109</v>
       </c>
       <c r="C47">
-        <v>9.79935417783614</v>
+        <v>9.612176519368827</v>
       </c>
       <c r="D47">
-        <v>6.664354177836138</v>
+        <v>6.654176519368828</v>
       </c>
       <c r="E47">
-        <v>7.965</v>
+        <v>8.141999999999999</v>
       </c>
       <c r="F47">
-        <v>7.965</v>
+        <v>8.141999999999999</v>
       </c>
       <c r="G47">
         <v>11.1</v>
@@ -5135,45 +5135,45 @@
         <v>4.074</v>
       </c>
       <c r="M47">
-        <v>0.412587</v>
+        <v>0.435597</v>
       </c>
       <c r="N47">
-        <v>3.661413</v>
+        <v>3.638403</v>
       </c>
       <c r="O47">
-        <v>0.58582608</v>
+        <v>0.58214448</v>
       </c>
       <c r="P47">
-        <v>3.07558692</v>
+        <v>3.05625852</v>
       </c>
       <c r="Q47">
-        <v>3.22158692</v>
+        <v>3.20225852</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.1076285308488222</v>
+        <v>0.108664928636039</v>
       </c>
       <c r="T47">
-        <v>0.8510929997011287</v>
+        <v>0.8653594053474599</v>
       </c>
       <c r="U47">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V47">
         <v>0.16</v>
       </c>
       <c r="W47">
-        <v>0.043512</v>
+        <v>0.04494</v>
       </c>
       <c r="X47" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y47">
-        <v>9.874281060721739</v>
+        <v>9.35268149229678</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5181,22 +5181,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.07935146146346109</v>
+        <v>0.07928423096006998</v>
       </c>
       <c r="C48">
-        <v>9.612176519368827</v>
+        <v>9.4363641493581</v>
       </c>
       <c r="D48">
-        <v>6.654176519368828</v>
+        <v>6.655364149358103</v>
       </c>
       <c r="E48">
-        <v>8.141999999999999</v>
+        <v>8.319000000000001</v>
       </c>
       <c r="F48">
-        <v>8.141999999999999</v>
+        <v>8.319000000000001</v>
       </c>
       <c r="G48">
         <v>11.1</v>
@@ -5217,28 +5217,28 @@
         <v>4.074</v>
       </c>
       <c r="M48">
-        <v>0.435597</v>
+        <v>0.4450665</v>
       </c>
       <c r="N48">
-        <v>3.638403</v>
+        <v>3.6289335</v>
       </c>
       <c r="O48">
-        <v>0.58214448</v>
+        <v>0.58062936</v>
       </c>
       <c r="P48">
-        <v>3.05625852</v>
+        <v>3.048304139999999</v>
       </c>
       <c r="Q48">
-        <v>3.20225852</v>
+        <v>3.194304139999999</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.108664928636039</v>
+        <v>0.1097404357737169</v>
       </c>
       <c r="T48">
-        <v>0.8653594053474599</v>
+        <v>0.8801641659238414</v>
       </c>
       <c r="U48">
         <v>0.0535</v>
@@ -5255,7 +5255,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>9.35268149229678</v>
+        <v>9.153688269056421</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5263,22 +5263,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.07928423096006998</v>
+        <v>0.07921700045667886</v>
       </c>
       <c r="C49">
-        <v>9.4363641493581</v>
+        <v>9.260552203356804</v>
       </c>
       <c r="D49">
-        <v>6.655364149358103</v>
+        <v>6.656552203356804</v>
       </c>
       <c r="E49">
-        <v>8.319000000000001</v>
+        <v>8.496</v>
       </c>
       <c r="F49">
-        <v>8.319000000000001</v>
+        <v>8.496</v>
       </c>
       <c r="G49">
         <v>11.1</v>
@@ -5299,28 +5299,28 @@
         <v>4.074</v>
       </c>
       <c r="M49">
-        <v>0.4450665</v>
+        <v>0.454536</v>
       </c>
       <c r="N49">
-        <v>3.6289335</v>
+        <v>3.619464</v>
       </c>
       <c r="O49">
-        <v>0.58062936</v>
+        <v>0.57911424</v>
       </c>
       <c r="P49">
-        <v>3.048304139999999</v>
+        <v>3.04034976</v>
       </c>
       <c r="Q49">
-        <v>3.194304139999999</v>
+        <v>3.18634976</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.1097404357737169</v>
+        <v>0.1108573085705362</v>
       </c>
       <c r="T49">
-        <v>0.8801641659238414</v>
+        <v>0.8955383403685453</v>
       </c>
       <c r="U49">
         <v>0.0535</v>
@@ -5337,7 +5337,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>9.153688269056421</v>
+        <v>8.962986430117745</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5345,22 +5345,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.07921700045667884</v>
+        <v>0.07914976995328771</v>
       </c>
       <c r="C50">
-        <v>9.260552203356806</v>
+        <v>9.08474068159204</v>
       </c>
       <c r="D50">
-        <v>6.656552203356804</v>
+        <v>6.657740681592039</v>
       </c>
       <c r="E50">
-        <v>8.495999999999999</v>
+        <v>8.673</v>
       </c>
       <c r="F50">
-        <v>8.495999999999999</v>
+        <v>8.673</v>
       </c>
       <c r="G50">
         <v>11.1</v>
@@ -5381,28 +5381,28 @@
         <v>4.074</v>
       </c>
       <c r="M50">
-        <v>0.4545359999999999</v>
+        <v>0.4640055</v>
       </c>
       <c r="N50">
-        <v>3.619464</v>
+        <v>3.6099945</v>
       </c>
       <c r="O50">
-        <v>0.57911424</v>
+        <v>0.57759912</v>
       </c>
       <c r="P50">
-        <v>3.04034976</v>
+        <v>3.03239538</v>
       </c>
       <c r="Q50">
-        <v>3.18634976</v>
+        <v>3.17839538</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.1108573085705362</v>
+        <v>0.1120179803005641</v>
       </c>
       <c r="T50">
-        <v>0.8955383403685452</v>
+        <v>0.911515423615002</v>
       </c>
       <c r="U50">
         <v>0.0535</v>
@@ -5419,7 +5419,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>8.962986430117747</v>
+        <v>8.78006833970718</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5427,22 +5427,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.07914976995328771</v>
+        <v>0.0790825394498966</v>
       </c>
       <c r="C51">
-        <v>9.08474068159204</v>
+        <v>8.908929584291082</v>
       </c>
       <c r="D51">
-        <v>6.657740681592039</v>
+        <v>6.65892958429108</v>
       </c>
       <c r="E51">
-        <v>8.673</v>
+        <v>8.85</v>
       </c>
       <c r="F51">
-        <v>8.673</v>
+        <v>8.85</v>
       </c>
       <c r="G51">
         <v>11.1</v>
@@ -5463,28 +5463,28 @@
         <v>4.074</v>
       </c>
       <c r="M51">
-        <v>0.4640055</v>
+        <v>0.473475</v>
       </c>
       <c r="N51">
-        <v>3.6099945</v>
+        <v>3.600525</v>
       </c>
       <c r="O51">
-        <v>0.57759912</v>
+        <v>0.5760839999999999</v>
       </c>
       <c r="P51">
-        <v>3.03239538</v>
+        <v>3.024441</v>
       </c>
       <c r="Q51">
-        <v>3.17839538</v>
+        <v>3.170441</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.1120179803005641</v>
+        <v>0.1132250788997932</v>
       </c>
       <c r="T51">
-        <v>0.911515423615002</v>
+        <v>0.9281315901913171</v>
       </c>
       <c r="U51">
         <v>0.0535</v>
@@ -5501,7 +5501,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>8.78006833970718</v>
+        <v>8.604466972913038</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5509,22 +5509,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.0790825394498966</v>
+        <v>0.07901530894650548</v>
       </c>
       <c r="C52">
-        <v>8.908929584291082</v>
+        <v>8.733118911681368</v>
       </c>
       <c r="D52">
-        <v>6.65892958429108</v>
+        <v>6.660118911681367</v>
       </c>
       <c r="E52">
-        <v>8.85</v>
+        <v>9.026999999999999</v>
       </c>
       <c r="F52">
-        <v>8.85</v>
+        <v>9.026999999999999</v>
       </c>
       <c r="G52">
         <v>11.1</v>
@@ -5545,28 +5545,28 @@
         <v>4.074</v>
       </c>
       <c r="M52">
-        <v>0.473475</v>
+        <v>0.4829444999999999</v>
       </c>
       <c r="N52">
-        <v>3.600525</v>
+        <v>3.5910555</v>
       </c>
       <c r="O52">
-        <v>0.5760839999999999</v>
+        <v>0.5745688800000001</v>
       </c>
       <c r="P52">
-        <v>3.024441</v>
+        <v>3.01648662</v>
       </c>
       <c r="Q52">
-        <v>3.170441</v>
+        <v>3.16248662</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.1132250788997932</v>
+        <v>0.114481446829603</v>
       </c>
       <c r="T52">
-        <v>0.9281315901913171</v>
+        <v>0.9454259676482983</v>
       </c>
       <c r="U52">
         <v>0.0535</v>
@@ -5583,7 +5583,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>8.604466972913038</v>
+        <v>8.435751934228467</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5591,22 +5591,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.07901530894650548</v>
+        <v>0.07894807844311434</v>
       </c>
       <c r="C53">
-        <v>8.733118911681368</v>
+        <v>8.557308663990497</v>
       </c>
       <c r="D53">
-        <v>6.660118911681367</v>
+        <v>6.661308663990496</v>
       </c>
       <c r="E53">
-        <v>9.026999999999999</v>
+        <v>9.204000000000001</v>
       </c>
       <c r="F53">
-        <v>9.026999999999999</v>
+        <v>9.204000000000001</v>
       </c>
       <c r="G53">
         <v>11.1</v>
@@ -5627,28 +5627,28 @@
         <v>4.074</v>
       </c>
       <c r="M53">
-        <v>0.4829444999999999</v>
+        <v>0.492414</v>
       </c>
       <c r="N53">
-        <v>3.5910555</v>
+        <v>3.581586</v>
       </c>
       <c r="O53">
-        <v>0.5745688800000001</v>
+        <v>0.57305376</v>
       </c>
       <c r="P53">
-        <v>3.01648662</v>
+        <v>3.00853224</v>
       </c>
       <c r="Q53">
-        <v>3.16248662</v>
+        <v>3.15453224</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.114481446829603</v>
+        <v>0.1157901634231549</v>
       </c>
       <c r="T53">
-        <v>0.9454259676482983</v>
+        <v>0.9634409441659869</v>
       </c>
       <c r="U53">
         <v>0.0535</v>
@@ -5665,7 +5665,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>8.435751934228467</v>
+        <v>8.273525935493304</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5673,22 +5673,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.07894807844311434</v>
+        <v>0.07888084793972322</v>
       </c>
       <c r="C54">
-        <v>8.557308663990497</v>
+        <v>8.381498841446227</v>
       </c>
       <c r="D54">
-        <v>6.661308663990496</v>
+        <v>6.662498841446229</v>
       </c>
       <c r="E54">
-        <v>9.204000000000001</v>
+        <v>9.381</v>
       </c>
       <c r="F54">
-        <v>9.204000000000001</v>
+        <v>9.381</v>
       </c>
       <c r="G54">
         <v>11.1</v>
@@ -5709,28 +5709,28 @@
         <v>4.074</v>
       </c>
       <c r="M54">
-        <v>0.492414</v>
+        <v>0.5018835</v>
       </c>
       <c r="N54">
-        <v>3.581586</v>
+        <v>3.5721165</v>
       </c>
       <c r="O54">
-        <v>0.57305376</v>
+        <v>0.57153864</v>
       </c>
       <c r="P54">
-        <v>3.00853224</v>
+        <v>3.00057786</v>
       </c>
       <c r="Q54">
-        <v>3.15453224</v>
+        <v>3.14657786</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.1157901634231549</v>
+        <v>0.1171545700845175</v>
       </c>
       <c r="T54">
-        <v>0.9634409441659869</v>
+        <v>0.9822225154291091</v>
       </c>
       <c r="U54">
         <v>0.0535</v>
@@ -5747,7 +5747,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>8.273525935493304</v>
+        <v>8.117421672559468</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5755,22 +5755,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.07888084793972322</v>
+        <v>0.0788136174363321</v>
       </c>
       <c r="C55">
-        <v>8.381498841446227</v>
+        <v>8.205689444276487</v>
       </c>
       <c r="D55">
-        <v>6.662498841446229</v>
+        <v>6.663689444276487</v>
       </c>
       <c r="E55">
-        <v>9.381</v>
+        <v>9.558</v>
       </c>
       <c r="F55">
-        <v>9.381</v>
+        <v>9.558</v>
       </c>
       <c r="G55">
         <v>11.1</v>
@@ -5791,28 +5791,28 @@
         <v>4.074</v>
       </c>
       <c r="M55">
-        <v>0.5018835</v>
+        <v>0.5113529999999999</v>
       </c>
       <c r="N55">
-        <v>3.5721165</v>
+        <v>3.562647</v>
       </c>
       <c r="O55">
-        <v>0.57153864</v>
+        <v>0.57002352</v>
       </c>
       <c r="P55">
-        <v>3.00057786</v>
+        <v>2.99262348</v>
       </c>
       <c r="Q55">
-        <v>3.14657786</v>
+        <v>3.13862348</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.1171545700845175</v>
+        <v>0.118578298774635</v>
       </c>
       <c r="T55">
-        <v>0.9822225154291091</v>
+        <v>1.00182067674715</v>
       </c>
       <c r="U55">
         <v>0.0535</v>
@@ -5829,7 +5829,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>8.117421672559468</v>
+        <v>7.967099048993553</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5837,22 +5837,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.0788136174363321</v>
+        <v>0.07874638693294098</v>
       </c>
       <c r="C56">
-        <v>8.205689444276487</v>
+        <v>8.02988047270936</v>
       </c>
       <c r="D56">
-        <v>6.663689444276487</v>
+        <v>6.664880472709362</v>
       </c>
       <c r="E56">
-        <v>9.558</v>
+        <v>9.735000000000001</v>
       </c>
       <c r="F56">
-        <v>9.558</v>
+        <v>9.735000000000001</v>
       </c>
       <c r="G56">
         <v>11.1</v>
@@ -5873,28 +5873,28 @@
         <v>4.074</v>
       </c>
       <c r="M56">
-        <v>0.5113529999999999</v>
+        <v>0.5208225000000001</v>
       </c>
       <c r="N56">
-        <v>3.562647</v>
+        <v>3.5531775</v>
       </c>
       <c r="O56">
-        <v>0.57002352</v>
+        <v>0.5685084</v>
       </c>
       <c r="P56">
-        <v>2.99262348</v>
+        <v>2.9846691</v>
       </c>
       <c r="Q56">
-        <v>3.13862348</v>
+        <v>3.1306691</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.118578298774635</v>
+        <v>0.1200653042954244</v>
       </c>
       <c r="T56">
-        <v>1.00182067674715</v>
+        <v>1.022289867457103</v>
       </c>
       <c r="U56">
         <v>0.0535</v>
@@ -5911,7 +5911,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>7.967099048993553</v>
+        <v>7.822242702648214</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5919,22 +5919,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.07874638693294098</v>
+        <v>0.07867915642954985</v>
       </c>
       <c r="C57">
-        <v>8.02988047270936</v>
+        <v>7.854071926973097</v>
       </c>
       <c r="D57">
-        <v>6.664880472709362</v>
+        <v>6.666071926973098</v>
       </c>
       <c r="E57">
-        <v>9.735000000000001</v>
+        <v>9.912000000000001</v>
       </c>
       <c r="F57">
-        <v>9.735000000000001</v>
+        <v>9.912000000000001</v>
       </c>
       <c r="G57">
         <v>11.1</v>
@@ -5955,28 +5955,28 @@
         <v>4.074</v>
       </c>
       <c r="M57">
-        <v>0.5208225000000001</v>
+        <v>0.530292</v>
       </c>
       <c r="N57">
-        <v>3.5531775</v>
+        <v>3.543708</v>
       </c>
       <c r="O57">
-        <v>0.5685084</v>
+        <v>0.5669932799999999</v>
       </c>
       <c r="P57">
-        <v>2.9846691</v>
+        <v>2.976714719999999</v>
       </c>
       <c r="Q57">
-        <v>3.1306691</v>
+        <v>3.122714719999999</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.1200653042954244</v>
+        <v>0.1216199009762497</v>
       </c>
       <c r="T57">
-        <v>1.022289867457103</v>
+        <v>1.0436894759266</v>
       </c>
       <c r="U57">
         <v>0.0535</v>
@@ -5993,7 +5993,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>7.822242702648214</v>
+        <v>7.682559797243782</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6001,22 +6001,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.07867915642954985</v>
+        <v>0.07899496592615872</v>
       </c>
       <c r="C58">
-        <v>7.854071926973097</v>
+        <v>7.671478869427352</v>
       </c>
       <c r="D58">
-        <v>6.666071926973098</v>
+        <v>6.660478869427352</v>
       </c>
       <c r="E58">
-        <v>9.912000000000001</v>
+        <v>10.089</v>
       </c>
       <c r="F58">
-        <v>9.912000000000001</v>
+        <v>10.089</v>
       </c>
       <c r="G58">
         <v>11.1</v>
@@ -6037,45 +6037,45 @@
         <v>4.074</v>
       </c>
       <c r="M58">
-        <v>0.530292</v>
+        <v>0.5478327000000001</v>
       </c>
       <c r="N58">
-        <v>3.543708</v>
+        <v>3.5261673</v>
       </c>
       <c r="O58">
-        <v>0.5669932799999999</v>
+        <v>0.564186768</v>
       </c>
       <c r="P58">
-        <v>2.976714719999999</v>
+        <v>2.961980532</v>
       </c>
       <c r="Q58">
-        <v>3.122714719999999</v>
+        <v>3.107980532</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.1216199009762497</v>
+        <v>0.1232468044794389</v>
       </c>
       <c r="T58">
-        <v>1.0436894759266</v>
+        <v>1.066084415022585</v>
       </c>
       <c r="U58">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V58">
         <v>0.16</v>
       </c>
       <c r="W58">
-        <v>0.04494</v>
+        <v>0.045612</v>
       </c>
       <c r="X58" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y58">
-        <v>7.682559797243782</v>
+        <v>7.436576896559843</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6083,22 +6083,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.07899496592615872</v>
+        <v>0.0789344554227676</v>
       </c>
       <c r="C59">
-        <v>7.671478869427352</v>
+        <v>7.495549797126353</v>
       </c>
       <c r="D59">
-        <v>6.660478869427352</v>
+        <v>6.661549797126352</v>
       </c>
       <c r="E59">
-        <v>10.089</v>
+        <v>10.266</v>
       </c>
       <c r="F59">
-        <v>10.089</v>
+        <v>10.266</v>
       </c>
       <c r="G59">
         <v>11.1</v>
@@ -6119,28 +6119,28 @@
         <v>4.074</v>
       </c>
       <c r="M59">
-        <v>0.5478327000000001</v>
+        <v>0.5574438</v>
       </c>
       <c r="N59">
-        <v>3.5261673</v>
+        <v>3.5165562</v>
       </c>
       <c r="O59">
-        <v>0.564186768</v>
+        <v>0.562648992</v>
       </c>
       <c r="P59">
-        <v>2.961980532</v>
+        <v>2.953907208</v>
       </c>
       <c r="Q59">
-        <v>3.107980532</v>
+        <v>3.099907207999999</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.1232468044794389</v>
+        <v>0.1249511795780181</v>
       </c>
       <c r="T59">
-        <v>1.066084415022585</v>
+        <v>1.089545779789807</v>
       </c>
       <c r="U59">
         <v>0.0543</v>
@@ -6157,7 +6157,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>7.436576896559843</v>
+        <v>7.308360053515708</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6165,22 +6165,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.07893445542276759</v>
+        <v>0.07887394491937647</v>
       </c>
       <c r="C60">
-        <v>7.495549797126355</v>
+        <v>7.319621069266224</v>
       </c>
       <c r="D60">
-        <v>6.661549797126353</v>
+        <v>6.662621069266225</v>
       </c>
       <c r="E60">
-        <v>10.266</v>
+        <v>10.443</v>
       </c>
       <c r="F60">
-        <v>10.266</v>
+        <v>10.443</v>
       </c>
       <c r="G60">
         <v>11.1</v>
@@ -6201,28 +6201,28 @@
         <v>4.074</v>
       </c>
       <c r="M60">
-        <v>0.5574437999999999</v>
+        <v>0.5670549</v>
       </c>
       <c r="N60">
-        <v>3.5165562</v>
+        <v>3.5069451</v>
       </c>
       <c r="O60">
-        <v>0.5626489920000001</v>
+        <v>0.561111216</v>
       </c>
       <c r="P60">
-        <v>2.953907208</v>
+        <v>2.945833884</v>
       </c>
       <c r="Q60">
-        <v>3.099907208</v>
+        <v>3.091833884</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.1249511795780181</v>
+        <v>0.1267386949253085</v>
       </c>
       <c r="T60">
-        <v>1.089545779789807</v>
+        <v>1.114151601374943</v>
       </c>
       <c r="U60">
         <v>0.0543</v>
@@ -6239,7 +6239,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>7.30836005351571</v>
+        <v>7.184489544134085</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6247,22 +6247,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.07887394491937647</v>
+        <v>0.07881343441598535</v>
       </c>
       <c r="C61">
-        <v>7.319621069266224</v>
+        <v>7.14369268601317</v>
       </c>
       <c r="D61">
-        <v>6.662621069266225</v>
+        <v>6.663692686013169</v>
       </c>
       <c r="E61">
-        <v>10.443</v>
+        <v>10.62</v>
       </c>
       <c r="F61">
-        <v>10.443</v>
+        <v>10.62</v>
       </c>
       <c r="G61">
         <v>11.1</v>
@@ -6283,28 +6283,28 @@
         <v>4.074</v>
       </c>
       <c r="M61">
-        <v>0.5670549</v>
+        <v>0.576666</v>
       </c>
       <c r="N61">
-        <v>3.5069451</v>
+        <v>3.497334</v>
       </c>
       <c r="O61">
-        <v>0.561111216</v>
+        <v>0.55957344</v>
       </c>
       <c r="P61">
-        <v>2.945833884</v>
+        <v>2.93776056</v>
       </c>
       <c r="Q61">
-        <v>3.091833884</v>
+        <v>3.08376056</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.1267386949253085</v>
+        <v>0.1286155860399634</v>
       </c>
       <c r="T61">
-        <v>1.114151601374943</v>
+        <v>1.139987714039335</v>
       </c>
       <c r="U61">
         <v>0.0543</v>
@@ -6321,7 +6321,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>7.184489544134085</v>
+        <v>7.064748051731851</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6329,22 +6329,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.07881343441598535</v>
+        <v>0.07875292391259422</v>
       </c>
       <c r="C62">
-        <v>7.14369268601317</v>
+        <v>6.967764647533491</v>
       </c>
       <c r="D62">
-        <v>6.663692686013169</v>
+        <v>6.664764647533489</v>
       </c>
       <c r="E62">
-        <v>10.62</v>
+        <v>10.797</v>
       </c>
       <c r="F62">
-        <v>10.62</v>
+        <v>10.797</v>
       </c>
       <c r="G62">
         <v>11.1</v>
@@ -6365,28 +6365,28 @@
         <v>4.074</v>
       </c>
       <c r="M62">
-        <v>0.576666</v>
+        <v>0.5862771</v>
       </c>
       <c r="N62">
-        <v>3.497334</v>
+        <v>3.4877229</v>
       </c>
       <c r="O62">
-        <v>0.55957344</v>
+        <v>0.5580356639999999</v>
       </c>
       <c r="P62">
-        <v>2.93776056</v>
+        <v>2.929687235999999</v>
       </c>
       <c r="Q62">
-        <v>3.08376056</v>
+        <v>3.075687235999999</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.1286155860399634</v>
+        <v>0.1305887279810108</v>
       </c>
       <c r="T62">
-        <v>1.139987714039335</v>
+        <v>1.167148755558312</v>
       </c>
       <c r="U62">
         <v>0.0543</v>
@@ -6403,7 +6403,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>7.064748051731851</v>
+        <v>6.948932509900182</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6411,22 +6411,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.07875292391259422</v>
+        <v>0.0786924134092031</v>
       </c>
       <c r="C63">
-        <v>6.967764647533491</v>
+        <v>6.791836953993599</v>
       </c>
       <c r="D63">
-        <v>6.664764647533489</v>
+        <v>6.6658369539936</v>
       </c>
       <c r="E63">
-        <v>10.797</v>
+        <v>10.974</v>
       </c>
       <c r="F63">
-        <v>10.797</v>
+        <v>10.974</v>
       </c>
       <c r="G63">
         <v>11.1</v>
@@ -6447,28 +6447,28 @@
         <v>4.074</v>
       </c>
       <c r="M63">
-        <v>0.5862771</v>
+        <v>0.5958882</v>
       </c>
       <c r="N63">
-        <v>3.4877229</v>
+        <v>3.4781118</v>
       </c>
       <c r="O63">
-        <v>0.5580356639999999</v>
+        <v>0.556497888</v>
       </c>
       <c r="P63">
-        <v>2.929687235999999</v>
+        <v>2.921613912</v>
       </c>
       <c r="Q63">
-        <v>3.075687235999999</v>
+        <v>3.067613912</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.1305887279810108</v>
+        <v>0.1326657194979029</v>
       </c>
       <c r="T63">
-        <v>1.167148755558312</v>
+        <v>1.195739325578287</v>
       </c>
       <c r="U63">
         <v>0.0543</v>
@@ -6485,7 +6485,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>6.948932509900182</v>
+        <v>6.836852953288888</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6493,22 +6493,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.0786924134092031</v>
+        <v>0.07863190290581198</v>
       </c>
       <c r="C64">
-        <v>6.791836953993599</v>
+        <v>6.615909605560024</v>
       </c>
       <c r="D64">
-        <v>6.6658369539936</v>
+        <v>6.666909605560025</v>
       </c>
       <c r="E64">
-        <v>10.974</v>
+        <v>11.151</v>
       </c>
       <c r="F64">
-        <v>10.974</v>
+        <v>11.151</v>
       </c>
       <c r="G64">
         <v>11.1</v>
@@ -6529,28 +6529,28 @@
         <v>4.074</v>
       </c>
       <c r="M64">
-        <v>0.5958882</v>
+        <v>0.6054993</v>
       </c>
       <c r="N64">
-        <v>3.4781118</v>
+        <v>3.4685007</v>
       </c>
       <c r="O64">
-        <v>0.556497888</v>
+        <v>0.5549601119999999</v>
       </c>
       <c r="P64">
-        <v>2.921613912</v>
+        <v>2.913540588</v>
       </c>
       <c r="Q64">
-        <v>3.067613912</v>
+        <v>3.059540588</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.1326657194979029</v>
+        <v>0.1348549808265189</v>
       </c>
       <c r="T64">
-        <v>1.195739325578287</v>
+        <v>1.225875331815559</v>
       </c>
       <c r="U64">
         <v>0.0543</v>
@@ -6567,7 +6567,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>6.836852953288888</v>
+        <v>6.728331477839859</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6575,22 +6575,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.07863190290581198</v>
+        <v>0.07857139240242085</v>
       </c>
       <c r="C65">
-        <v>6.615909605560024</v>
+        <v>6.43998260239939</v>
       </c>
       <c r="D65">
-        <v>6.666909605560025</v>
+        <v>6.667982602399389</v>
       </c>
       <c r="E65">
-        <v>11.151</v>
+        <v>11.328</v>
       </c>
       <c r="F65">
-        <v>11.151</v>
+        <v>11.328</v>
       </c>
       <c r="G65">
         <v>11.1</v>
@@ -6611,28 +6611,28 @@
         <v>4.074</v>
       </c>
       <c r="M65">
-        <v>0.6054993</v>
+        <v>0.6151103999999999</v>
       </c>
       <c r="N65">
-        <v>3.4685007</v>
+        <v>3.4588896</v>
       </c>
       <c r="O65">
-        <v>0.5549601119999999</v>
+        <v>0.553422336</v>
       </c>
       <c r="P65">
-        <v>2.913540588</v>
+        <v>2.905467264</v>
       </c>
       <c r="Q65">
-        <v>3.059540588</v>
+        <v>3.051467264</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.1348549808265189</v>
+        <v>0.1371658677845023</v>
       </c>
       <c r="T65">
-        <v>1.225875331815559</v>
+        <v>1.257685560621567</v>
       </c>
       <c r="U65">
         <v>0.0543</v>
@@ -6649,7 +6649,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>6.728331477839859</v>
+        <v>6.623201298498612</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6657,22 +6657,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.07857139240242085</v>
+        <v>0.07851088189902973</v>
       </c>
       <c r="C66">
-        <v>6.43998260239939</v>
+        <v>6.264055944678427</v>
       </c>
       <c r="D66">
-        <v>6.667982602399389</v>
+        <v>6.669055944678428</v>
       </c>
       <c r="E66">
-        <v>11.328</v>
+        <v>11.505</v>
       </c>
       <c r="F66">
-        <v>11.328</v>
+        <v>11.505</v>
       </c>
       <c r="G66">
         <v>11.1</v>
@@ -6693,28 +6693,28 @@
         <v>4.074</v>
       </c>
       <c r="M66">
-        <v>0.6151103999999999</v>
+        <v>0.6247215</v>
       </c>
       <c r="N66">
-        <v>3.4588896</v>
+        <v>3.4492785</v>
       </c>
       <c r="O66">
-        <v>0.553422336</v>
+        <v>0.55188456</v>
       </c>
       <c r="P66">
-        <v>2.905467264</v>
+        <v>2.89739394</v>
       </c>
       <c r="Q66">
-        <v>3.051467264</v>
+        <v>3.04339394</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.1371658677845023</v>
+        <v>0.1396088054257992</v>
       </c>
       <c r="T66">
-        <v>1.257685560621567</v>
+        <v>1.29131351678792</v>
       </c>
       <c r="U66">
         <v>0.0543</v>
@@ -6731,7 +6731,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>6.623201298498612</v>
+        <v>6.521305893906324</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6739,22 +6739,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.07851088189902973</v>
+        <v>0.07845037139563861</v>
       </c>
       <c r="C67">
-        <v>6.264055944678427</v>
+        <v>6.088129632563986</v>
       </c>
       <c r="D67">
-        <v>6.669055944678428</v>
+        <v>6.670129632563987</v>
       </c>
       <c r="E67">
-        <v>11.505</v>
+        <v>11.682</v>
       </c>
       <c r="F67">
-        <v>11.505</v>
+        <v>11.682</v>
       </c>
       <c r="G67">
         <v>11.1</v>
@@ -6775,28 +6775,28 @@
         <v>4.074</v>
       </c>
       <c r="M67">
-        <v>0.6247215</v>
+        <v>0.6343326</v>
       </c>
       <c r="N67">
-        <v>3.4492785</v>
+        <v>3.4396674</v>
       </c>
       <c r="O67">
-        <v>0.55188456</v>
+        <v>0.550346784</v>
       </c>
       <c r="P67">
-        <v>2.89739394</v>
+        <v>2.889320616</v>
       </c>
       <c r="Q67">
-        <v>3.04339394</v>
+        <v>3.035320616</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.1396088054257992</v>
+        <v>0.14219544528129</v>
       </c>
       <c r="T67">
-        <v>1.29131351678792</v>
+        <v>1.326919588022881</v>
       </c>
       <c r="U67">
         <v>0.0543</v>
@@ -6813,7 +6813,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>6.521305893906324</v>
+        <v>6.422498228847138</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6821,22 +6821,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.07845037139563861</v>
+        <v>0.07838986089224748</v>
       </c>
       <c r="C68">
-        <v>6.088129632563986</v>
+        <v>5.912203666223013</v>
       </c>
       <c r="D68">
-        <v>6.670129632563987</v>
+        <v>6.671203666223013</v>
       </c>
       <c r="E68">
-        <v>11.682</v>
+        <v>11.859</v>
       </c>
       <c r="F68">
-        <v>11.682</v>
+        <v>11.859</v>
       </c>
       <c r="G68">
         <v>11.1</v>
@@ -6857,28 +6857,28 @@
         <v>4.074</v>
       </c>
       <c r="M68">
-        <v>0.6343326</v>
+        <v>0.6439437</v>
       </c>
       <c r="N68">
-        <v>3.4396674</v>
+        <v>3.4300563</v>
       </c>
       <c r="O68">
-        <v>0.550346784</v>
+        <v>0.548809008</v>
       </c>
       <c r="P68">
-        <v>2.889320616</v>
+        <v>2.881247292</v>
       </c>
       <c r="Q68">
-        <v>3.035320616</v>
+        <v>3.027247292</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.14219544528129</v>
+        <v>0.1449388511886287</v>
       </c>
       <c r="T68">
-        <v>1.326919588022881</v>
+        <v>1.364683602969052</v>
       </c>
       <c r="U68">
         <v>0.0543</v>
@@ -6895,7 +6895,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>6.422498228847138</v>
+        <v>6.326640046327031</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6903,22 +6903,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.07838986089224748</v>
+        <v>0.07832935038885636</v>
       </c>
       <c r="C69">
-        <v>5.912203666223013</v>
+        <v>5.736278045822564</v>
       </c>
       <c r="D69">
-        <v>6.671203666223013</v>
+        <v>6.672278045822565</v>
       </c>
       <c r="E69">
-        <v>11.859</v>
+        <v>12.036</v>
       </c>
       <c r="F69">
-        <v>11.859</v>
+        <v>12.036</v>
       </c>
       <c r="G69">
         <v>11.1</v>
@@ -6939,28 +6939,28 @@
         <v>4.074</v>
       </c>
       <c r="M69">
-        <v>0.6439437</v>
+        <v>0.6535548</v>
       </c>
       <c r="N69">
-        <v>3.4300563</v>
+        <v>3.4204452</v>
       </c>
       <c r="O69">
-        <v>0.548809008</v>
+        <v>0.5472712319999999</v>
       </c>
       <c r="P69">
-        <v>2.881247292</v>
+        <v>2.873173968</v>
       </c>
       <c r="Q69">
-        <v>3.027247292</v>
+        <v>3.019173968</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.1449388511886287</v>
+        <v>0.1478537199651761</v>
       </c>
       <c r="T69">
-        <v>1.364683602969052</v>
+        <v>1.404807868849358</v>
       </c>
       <c r="U69">
         <v>0.0543</v>
@@ -6977,7 +6977,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>6.326640046327031</v>
+        <v>6.233601222116339</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6985,22 +6985,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.07832935038885636</v>
+        <v>0.07826883988546524</v>
       </c>
       <c r="C70">
-        <v>5.736278045822564</v>
+        <v>5.560352771529807</v>
       </c>
       <c r="D70">
-        <v>6.672278045822565</v>
+        <v>6.673352771529808</v>
       </c>
       <c r="E70">
-        <v>12.036</v>
+        <v>12.213</v>
       </c>
       <c r="F70">
-        <v>12.036</v>
+        <v>12.213</v>
       </c>
       <c r="G70">
         <v>11.1</v>
@@ -7021,28 +7021,28 @@
         <v>4.074</v>
       </c>
       <c r="M70">
-        <v>0.6535548</v>
+        <v>0.6631659000000001</v>
       </c>
       <c r="N70">
-        <v>3.4204452</v>
+        <v>3.4108341</v>
       </c>
       <c r="O70">
-        <v>0.5472712319999999</v>
+        <v>0.545733456</v>
       </c>
       <c r="P70">
-        <v>2.873173968</v>
+        <v>2.865100644</v>
       </c>
       <c r="Q70">
-        <v>3.019173968</v>
+        <v>3.011100644</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.1478537199651761</v>
+        <v>0.1509566447918233</v>
       </c>
       <c r="T70">
-        <v>1.404807868849358</v>
+        <v>1.447520797044523</v>
       </c>
       <c r="U70">
         <v>0.0543</v>
@@ -7059,7 +7059,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>6.233601222116339</v>
+        <v>6.143259175419001</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7067,22 +7067,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.07826883988546524</v>
+        <v>0.07879632938207409</v>
       </c>
       <c r="C71">
-        <v>5.560352771529807</v>
+        <v>5.373995671801449</v>
       </c>
       <c r="D71">
-        <v>6.673352771529808</v>
+        <v>6.66399567180145</v>
       </c>
       <c r="E71">
-        <v>12.213</v>
+        <v>12.39</v>
       </c>
       <c r="F71">
-        <v>12.213</v>
+        <v>12.39</v>
       </c>
       <c r="G71">
         <v>11.1</v>
@@ -7103,45 +7103,45 @@
         <v>4.074</v>
       </c>
       <c r="M71">
-        <v>0.6631659000000001</v>
+        <v>0.6851670000000001</v>
       </c>
       <c r="N71">
-        <v>3.4108341</v>
+        <v>3.388833</v>
       </c>
       <c r="O71">
-        <v>0.545733456</v>
+        <v>0.54221328</v>
       </c>
       <c r="P71">
-        <v>2.865100644</v>
+        <v>2.84661972</v>
       </c>
       <c r="Q71">
-        <v>3.011100644</v>
+        <v>2.99261972</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.1509566447918233</v>
+        <v>0.1542664312735804</v>
       </c>
       <c r="T71">
-        <v>1.447520797044523</v>
+        <v>1.493081253786032</v>
       </c>
       <c r="U71">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V71">
         <v>0.16</v>
       </c>
       <c r="W71">
-        <v>0.045612</v>
+        <v>0.046452</v>
       </c>
       <c r="X71" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y71">
-        <v>6.143259175419001</v>
+        <v>5.945995647776381</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7149,22 +7149,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.07879632938207409</v>
+        <v>0.07874421887868299</v>
       </c>
       <c r="C72">
-        <v>5.373995671801449</v>
+        <v>5.197918888168875</v>
       </c>
       <c r="D72">
-        <v>6.66399567180145</v>
+        <v>6.664918888168875</v>
       </c>
       <c r="E72">
-        <v>12.39</v>
+        <v>12.567</v>
       </c>
       <c r="F72">
-        <v>12.39</v>
+        <v>12.567</v>
       </c>
       <c r="G72">
         <v>11.1</v>
@@ -7185,28 +7185,28 @@
         <v>4.074</v>
       </c>
       <c r="M72">
-        <v>0.6851670000000001</v>
+        <v>0.6949551</v>
       </c>
       <c r="N72">
-        <v>3.388833</v>
+        <v>3.3790449</v>
       </c>
       <c r="O72">
-        <v>0.54221328</v>
+        <v>0.540647184</v>
       </c>
       <c r="P72">
-        <v>2.84661972</v>
+        <v>2.838397716</v>
       </c>
       <c r="Q72">
-        <v>2.99261972</v>
+        <v>2.984397716</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.1542664312735804</v>
+        <v>0.1578044788920103</v>
       </c>
       <c r="T72">
-        <v>1.493081253786032</v>
+        <v>1.541783810992474</v>
       </c>
       <c r="U72">
         <v>0.0553</v>
@@ -7223,7 +7223,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>5.945995647776381</v>
+        <v>5.862249230202066</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7231,22 +7231,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.07874421887868298</v>
+        <v>0.07869210837529186</v>
       </c>
       <c r="C73">
-        <v>5.197918888168877</v>
+        <v>5.021842360372769</v>
       </c>
       <c r="D73">
-        <v>6.664918888168875</v>
+        <v>6.665842360372769</v>
       </c>
       <c r="E73">
-        <v>12.567</v>
+        <v>12.744</v>
       </c>
       <c r="F73">
-        <v>12.567</v>
+        <v>12.744</v>
       </c>
       <c r="G73">
         <v>11.1</v>
@@ -7267,28 +7267,28 @@
         <v>4.074</v>
       </c>
       <c r="M73">
-        <v>0.6949550999999999</v>
+        <v>0.7047432</v>
       </c>
       <c r="N73">
-        <v>3.3790449</v>
+        <v>3.3692568</v>
       </c>
       <c r="O73">
-        <v>0.540647184</v>
+        <v>0.539081088</v>
       </c>
       <c r="P73">
-        <v>2.838397716</v>
+        <v>2.830175712</v>
       </c>
       <c r="Q73">
-        <v>2.984397716</v>
+        <v>2.976175711999999</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.1578044788920103</v>
+        <v>0.1615952441974709</v>
       </c>
       <c r="T73">
-        <v>1.541783810992473</v>
+        <v>1.593965122285088</v>
       </c>
       <c r="U73">
         <v>0.0553</v>
@@ -7305,7 +7305,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>5.862249230202067</v>
+        <v>5.780829102004815</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7313,22 +7313,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.07869210837529186</v>
+        <v>0.07863999787190072</v>
       </c>
       <c r="C74">
-        <v>5.021842360372769</v>
+        <v>4.84576608851949</v>
       </c>
       <c r="D74">
-        <v>6.665842360372769</v>
+        <v>6.666766088519489</v>
       </c>
       <c r="E74">
-        <v>12.744</v>
+        <v>12.921</v>
       </c>
       <c r="F74">
-        <v>12.744</v>
+        <v>12.921</v>
       </c>
       <c r="G74">
         <v>11.1</v>
@@ -7349,28 +7349,28 @@
         <v>4.074</v>
       </c>
       <c r="M74">
-        <v>0.7047432</v>
+        <v>0.7145313</v>
       </c>
       <c r="N74">
-        <v>3.3692568</v>
+        <v>3.3594687</v>
       </c>
       <c r="O74">
-        <v>0.539081088</v>
+        <v>0.537514992</v>
       </c>
       <c r="P74">
-        <v>2.830175712</v>
+        <v>2.821953708</v>
       </c>
       <c r="Q74">
-        <v>2.976175711999999</v>
+        <v>2.967953708</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.1615952441974709</v>
+        <v>0.1656668069329656</v>
       </c>
       <c r="T74">
-        <v>1.593965122285088</v>
+        <v>1.650011715895675</v>
       </c>
       <c r="U74">
         <v>0.0553</v>
@@ -7387,7 +7387,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>5.780829102004815</v>
+        <v>5.701639662251325</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7395,22 +7395,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.07863999787190072</v>
+        <v>0.07858788736850961</v>
       </c>
       <c r="C75">
-        <v>4.84576608851949</v>
+        <v>4.669690072715454</v>
       </c>
       <c r="D75">
-        <v>6.666766088519489</v>
+        <v>6.667690072715454</v>
       </c>
       <c r="E75">
-        <v>12.921</v>
+        <v>13.098</v>
       </c>
       <c r="F75">
-        <v>12.921</v>
+        <v>13.098</v>
       </c>
       <c r="G75">
         <v>11.1</v>
@@ -7431,28 +7431,28 @@
         <v>4.074</v>
       </c>
       <c r="M75">
-        <v>0.7145313</v>
+        <v>0.7243193999999999</v>
       </c>
       <c r="N75">
-        <v>3.3594687</v>
+        <v>3.3496806</v>
       </c>
       <c r="O75">
-        <v>0.537514992</v>
+        <v>0.5359488960000001</v>
       </c>
       <c r="P75">
-        <v>2.821953708</v>
+        <v>2.813731704</v>
       </c>
       <c r="Q75">
-        <v>2.967953708</v>
+        <v>2.959731704</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.1656668069329656</v>
+        <v>0.17005156680196</v>
       </c>
       <c r="T75">
-        <v>1.650011715895675</v>
+        <v>1.710369585937845</v>
       </c>
       <c r="U75">
         <v>0.0553</v>
@@ -7469,7 +7469,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>5.701639662251325</v>
+        <v>5.624590477626307</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7477,22 +7477,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.07858788736850961</v>
+        <v>0.07853577686511848</v>
       </c>
       <c r="C76">
-        <v>4.669690072715454</v>
+        <v>4.493614313067141</v>
       </c>
       <c r="D76">
-        <v>6.667690072715454</v>
+        <v>6.668614313067138</v>
       </c>
       <c r="E76">
-        <v>13.098</v>
+        <v>13.275</v>
       </c>
       <c r="F76">
-        <v>13.098</v>
+        <v>13.275</v>
       </c>
       <c r="G76">
         <v>11.1</v>
@@ -7513,28 +7513,28 @@
         <v>4.074</v>
       </c>
       <c r="M76">
-        <v>0.7243193999999999</v>
+        <v>0.7341074999999999</v>
       </c>
       <c r="N76">
-        <v>3.3496806</v>
+        <v>3.3398925</v>
       </c>
       <c r="O76">
-        <v>0.5359488960000001</v>
+        <v>0.5343828</v>
       </c>
       <c r="P76">
-        <v>2.813731704</v>
+        <v>2.8055097</v>
       </c>
       <c r="Q76">
-        <v>2.959731704</v>
+        <v>2.9515097</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.17005156680196</v>
+        <v>0.1747871074604739</v>
       </c>
       <c r="T76">
-        <v>1.710369585937845</v>
+        <v>1.775556085583389</v>
       </c>
       <c r="U76">
         <v>0.0553</v>
@@ -7551,7 +7551,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>5.624590477626307</v>
+        <v>5.549595937924623</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7559,22 +7559,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.07853577686511848</v>
+        <v>0.07848366636172735</v>
       </c>
       <c r="C77">
-        <v>4.493614313067141</v>
+        <v>4.31753880968108</v>
       </c>
       <c r="D77">
-        <v>6.668614313067138</v>
+        <v>6.66953880968108</v>
       </c>
       <c r="E77">
-        <v>13.275</v>
+        <v>13.452</v>
       </c>
       <c r="F77">
-        <v>13.275</v>
+        <v>13.452</v>
       </c>
       <c r="G77">
         <v>11.1</v>
@@ -7595,28 +7595,28 @@
         <v>4.074</v>
       </c>
       <c r="M77">
-        <v>0.7341074999999999</v>
+        <v>0.7438956</v>
       </c>
       <c r="N77">
-        <v>3.3398925</v>
+        <v>3.3301044</v>
       </c>
       <c r="O77">
-        <v>0.5343828</v>
+        <v>0.5328167039999999</v>
       </c>
       <c r="P77">
-        <v>2.8055097</v>
+        <v>2.797287696</v>
       </c>
       <c r="Q77">
-        <v>2.9515097</v>
+        <v>2.943287696</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.1747871074604739</v>
+        <v>0.1799172765071973</v>
       </c>
       <c r="T77">
-        <v>1.775556085583389</v>
+        <v>1.846174793532729</v>
       </c>
       <c r="U77">
         <v>0.0553</v>
@@ -7633,7 +7633,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>5.549595937924623</v>
+        <v>5.476574938741404</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7641,22 +7641,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.07848366636172735</v>
+        <v>0.07843155585833622</v>
       </c>
       <c r="C78">
-        <v>4.31753880968108</v>
+        <v>4.141463562663871</v>
       </c>
       <c r="D78">
-        <v>6.66953880968108</v>
+        <v>6.670463562663871</v>
       </c>
       <c r="E78">
-        <v>13.452</v>
+        <v>13.629</v>
       </c>
       <c r="F78">
-        <v>13.452</v>
+        <v>13.629</v>
       </c>
       <c r="G78">
         <v>11.1</v>
@@ -7677,28 +7677,28 @@
         <v>4.074</v>
       </c>
       <c r="M78">
-        <v>0.7438956</v>
+        <v>0.7536837</v>
       </c>
       <c r="N78">
-        <v>3.3301044</v>
+        <v>3.3203163</v>
       </c>
       <c r="O78">
-        <v>0.5328167039999999</v>
+        <v>0.531250608</v>
       </c>
       <c r="P78">
-        <v>2.797287696</v>
+        <v>2.789065692</v>
       </c>
       <c r="Q78">
-        <v>2.943287696</v>
+        <v>2.935065692</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.1799172765071973</v>
+        <v>0.1854935472101575</v>
       </c>
       <c r="T78">
-        <v>1.846174793532729</v>
+        <v>1.922934258695054</v>
       </c>
       <c r="U78">
         <v>0.0553</v>
@@ -7715,7 +7715,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>5.476574938741404</v>
+        <v>5.40545058888762</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7723,22 +7723,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.07843155585833622</v>
+        <v>0.07837944535494511</v>
       </c>
       <c r="C79">
-        <v>4.141463562663871</v>
+        <v>3.965388572122171</v>
       </c>
       <c r="D79">
-        <v>6.670463562663871</v>
+        <v>6.67138857212217</v>
       </c>
       <c r="E79">
-        <v>13.629</v>
+        <v>13.806</v>
       </c>
       <c r="F79">
-        <v>13.629</v>
+        <v>13.806</v>
       </c>
       <c r="G79">
         <v>11.1</v>
@@ -7759,28 +7759,28 @@
         <v>4.074</v>
       </c>
       <c r="M79">
-        <v>0.7536837</v>
+        <v>0.7634718</v>
       </c>
       <c r="N79">
-        <v>3.3203163</v>
+        <v>3.3105282</v>
       </c>
       <c r="O79">
-        <v>0.531250608</v>
+        <v>0.529684512</v>
       </c>
       <c r="P79">
-        <v>2.789065692</v>
+        <v>2.780843688</v>
       </c>
       <c r="Q79">
-        <v>2.935065692</v>
+        <v>2.926843688</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.1854935472101575</v>
+        <v>0.1915767516133869</v>
       </c>
       <c r="T79">
-        <v>1.922934258695054</v>
+        <v>2.006671857053955</v>
       </c>
       <c r="U79">
         <v>0.0553</v>
@@ -7797,7 +7797,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>5.40545058888762</v>
+        <v>5.336149940312136</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7805,22 +7805,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.07837944535494511</v>
+        <v>0.07832733485155398</v>
       </c>
       <c r="C80">
-        <v>3.965388572122171</v>
+        <v>3.789313838162684</v>
       </c>
       <c r="D80">
-        <v>6.67138857212217</v>
+        <v>6.672313838162684</v>
       </c>
       <c r="E80">
-        <v>13.806</v>
+        <v>13.983</v>
       </c>
       <c r="F80">
-        <v>13.806</v>
+        <v>13.983</v>
       </c>
       <c r="G80">
         <v>11.1</v>
@@ -7841,28 +7841,28 @@
         <v>4.074</v>
       </c>
       <c r="M80">
-        <v>0.7634718</v>
+        <v>0.7732599000000001</v>
       </c>
       <c r="N80">
-        <v>3.3105282</v>
+        <v>3.3007401</v>
       </c>
       <c r="O80">
-        <v>0.529684512</v>
+        <v>0.528118416</v>
       </c>
       <c r="P80">
-        <v>2.780843688</v>
+        <v>2.772621684</v>
       </c>
       <c r="Q80">
-        <v>2.926843688</v>
+        <v>2.918621684</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.1915767516133869</v>
+        <v>0.1982393088169238</v>
       </c>
       <c r="T80">
-        <v>2.006671857053955</v>
+        <v>2.09838446478037</v>
       </c>
       <c r="U80">
         <v>0.0553</v>
@@ -7879,7 +7879,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>5.336149940312136</v>
+        <v>5.268603738536033</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7887,22 +7887,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.07832733485155398</v>
+        <v>0.07827522434816286</v>
       </c>
       <c r="C81">
-        <v>3.789313838162684</v>
+        <v>3.613239360892191</v>
       </c>
       <c r="D81">
-        <v>6.672313838162684</v>
+        <v>6.67323936089219</v>
       </c>
       <c r="E81">
-        <v>13.983</v>
+        <v>14.16</v>
       </c>
       <c r="F81">
-        <v>13.983</v>
+        <v>14.16</v>
       </c>
       <c r="G81">
         <v>11.1</v>
@@ -7923,28 +7923,28 @@
         <v>4.074</v>
       </c>
       <c r="M81">
-        <v>0.7732599000000001</v>
+        <v>0.7830480000000001</v>
       </c>
       <c r="N81">
-        <v>3.3007401</v>
+        <v>3.290952</v>
       </c>
       <c r="O81">
-        <v>0.528118416</v>
+        <v>0.52655232</v>
       </c>
       <c r="P81">
-        <v>2.772621684</v>
+        <v>2.76439968</v>
       </c>
       <c r="Q81">
-        <v>2.918621684</v>
+        <v>2.91039968</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.1982393088169238</v>
+        <v>0.2055681217408143</v>
       </c>
       <c r="T81">
-        <v>2.09838446478037</v>
+        <v>2.199268333279426</v>
       </c>
       <c r="U81">
         <v>0.0553</v>
@@ -7961,7 +7961,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>5.268603738536033</v>
+        <v>5.202746191804334</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7969,22 +7969,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.07827522434816286</v>
+        <v>0.07822311384477174</v>
       </c>
       <c r="C82">
-        <v>3.613239360892191</v>
+        <v>3.43716514041752</v>
       </c>
       <c r="D82">
-        <v>6.67323936089219</v>
+        <v>6.674165140417519</v>
       </c>
       <c r="E82">
-        <v>14.16</v>
+        <v>14.337</v>
       </c>
       <c r="F82">
-        <v>14.16</v>
+        <v>14.337</v>
       </c>
       <c r="G82">
         <v>11.1</v>
@@ -8005,28 +8005,28 @@
         <v>4.074</v>
       </c>
       <c r="M82">
-        <v>0.7830480000000001</v>
+        <v>0.7928361</v>
       </c>
       <c r="N82">
-        <v>3.290952</v>
+        <v>3.2811639</v>
       </c>
       <c r="O82">
-        <v>0.52655232</v>
+        <v>0.5249862239999999</v>
       </c>
       <c r="P82">
-        <v>2.76439968</v>
+        <v>2.756177676</v>
       </c>
       <c r="Q82">
-        <v>2.91039968</v>
+        <v>2.902177676</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.2055681217408143</v>
+        <v>0.2136683886566934</v>
       </c>
       <c r="T82">
-        <v>2.199268333279426</v>
+        <v>2.31077155635733</v>
       </c>
       <c r="U82">
         <v>0.0553</v>
@@ -8043,7 +8043,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>5.202746191804334</v>
+        <v>5.138514757337613</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8051,22 +8051,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.07822311384477174</v>
+        <v>0.07817100334138061</v>
       </c>
       <c r="C83">
-        <v>3.43716514041752</v>
+        <v>3.261091176845559</v>
       </c>
       <c r="D83">
-        <v>6.674165140417519</v>
+        <v>6.67509117684556</v>
       </c>
       <c r="E83">
-        <v>14.337</v>
+        <v>14.514</v>
       </c>
       <c r="F83">
-        <v>14.337</v>
+        <v>14.514</v>
       </c>
       <c r="G83">
         <v>11.1</v>
@@ -8087,28 +8087,28 @@
         <v>4.074</v>
       </c>
       <c r="M83">
-        <v>0.7928361</v>
+        <v>0.8026242000000001</v>
       </c>
       <c r="N83">
-        <v>3.2811639</v>
+        <v>3.2713758</v>
       </c>
       <c r="O83">
-        <v>0.5249862239999999</v>
+        <v>0.5234201279999999</v>
       </c>
       <c r="P83">
-        <v>2.756177676</v>
+        <v>2.747955672</v>
       </c>
       <c r="Q83">
-        <v>2.902177676</v>
+        <v>2.893955672</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.2136683886566934</v>
+        <v>0.2226686852298923</v>
       </c>
       <c r="T83">
-        <v>2.31077155635733</v>
+        <v>2.434664026443891</v>
       </c>
       <c r="U83">
         <v>0.0553</v>
@@ -8125,7 +8125,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>5.138514757337613</v>
+        <v>5.075849943223739</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8133,22 +8133,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.07817100334138061</v>
+        <v>0.07811889283798948</v>
       </c>
       <c r="C84">
-        <v>3.261091176845559</v>
+        <v>3.08501747028326</v>
       </c>
       <c r="D84">
-        <v>6.67509117684556</v>
+        <v>6.676017470283262</v>
       </c>
       <c r="E84">
-        <v>14.514</v>
+        <v>14.691</v>
       </c>
       <c r="F84">
-        <v>14.514</v>
+        <v>14.691</v>
       </c>
       <c r="G84">
         <v>11.1</v>
@@ -8169,28 +8169,28 @@
         <v>4.074</v>
       </c>
       <c r="M84">
-        <v>0.8026242000000001</v>
+        <v>0.8124123000000001</v>
       </c>
       <c r="N84">
-        <v>3.2713758</v>
+        <v>3.2615877</v>
       </c>
       <c r="O84">
-        <v>0.5234201279999999</v>
+        <v>0.521854032</v>
       </c>
       <c r="P84">
-        <v>2.747955672</v>
+        <v>2.739733668</v>
       </c>
       <c r="Q84">
-        <v>2.893955672</v>
+        <v>2.885733667999999</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.2226686852298923</v>
+        <v>0.2327278402234676</v>
       </c>
       <c r="T84">
-        <v>2.434664026443891</v>
+        <v>2.573132081246517</v>
       </c>
       <c r="U84">
         <v>0.0553</v>
@@ -8207,7 +8207,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>5.075849943223739</v>
+        <v>5.014695124630682</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8215,22 +8215,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.07811889283798948</v>
+        <v>0.07806678233459835</v>
       </c>
       <c r="C85">
-        <v>3.08501747028326</v>
+        <v>2.908944020837639</v>
       </c>
       <c r="D85">
-        <v>6.676017470283262</v>
+        <v>6.676944020837639</v>
       </c>
       <c r="E85">
-        <v>14.691</v>
+        <v>14.868</v>
       </c>
       <c r="F85">
-        <v>14.691</v>
+        <v>14.868</v>
       </c>
       <c r="G85">
         <v>11.1</v>
@@ -8251,28 +8251,28 @@
         <v>4.074</v>
       </c>
       <c r="M85">
-        <v>0.8124123000000001</v>
+        <v>0.8222004000000001</v>
       </c>
       <c r="N85">
-        <v>3.2615877</v>
+        <v>3.2517996</v>
       </c>
       <c r="O85">
-        <v>0.521854032</v>
+        <v>0.520287936</v>
       </c>
       <c r="P85">
-        <v>2.739733668</v>
+        <v>2.731511664</v>
       </c>
       <c r="Q85">
-        <v>2.885733667999999</v>
+        <v>2.877511664</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.2327278402234676</v>
+        <v>0.2440443895912399</v>
       </c>
       <c r="T85">
-        <v>2.573132081246517</v>
+        <v>2.728908642899472</v>
       </c>
       <c r="U85">
         <v>0.0553</v>
@@ -8289,7 +8289,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>5.014695124630682</v>
+        <v>4.954996373146985</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8297,22 +8297,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.07806678233459836</v>
+        <v>0.07801467183120722</v>
       </c>
       <c r="C86">
-        <v>2.908944020837641</v>
+        <v>2.732870828615756</v>
       </c>
       <c r="D86">
-        <v>6.676944020837639</v>
+        <v>6.677870828615755</v>
       </c>
       <c r="E86">
-        <v>14.868</v>
+        <v>15.045</v>
       </c>
       <c r="F86">
-        <v>14.868</v>
+        <v>15.045</v>
       </c>
       <c r="G86">
         <v>11.1</v>
@@ -8333,28 +8333,28 @@
         <v>4.074</v>
       </c>
       <c r="M86">
-        <v>0.8222003999999999</v>
+        <v>0.8319884999999999</v>
       </c>
       <c r="N86">
-        <v>3.2517996</v>
+        <v>3.2420115</v>
       </c>
       <c r="O86">
-        <v>0.520287936</v>
+        <v>0.51872184</v>
       </c>
       <c r="P86">
-        <v>2.731511664</v>
+        <v>2.72328966</v>
       </c>
       <c r="Q86">
-        <v>2.877511664</v>
+        <v>2.86928966</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.2440443895912397</v>
+        <v>0.2568698122080482</v>
       </c>
       <c r="T86">
-        <v>2.72890864289947</v>
+        <v>2.905455412772818</v>
       </c>
       <c r="U86">
         <v>0.0553</v>
@@ -8371,7 +8371,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>4.954996373146985</v>
+        <v>4.896702298168785</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8379,22 +8379,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.07801467183120722</v>
+        <v>0.07796256132781612</v>
       </c>
       <c r="C87">
-        <v>2.732870828615756</v>
+        <v>2.556797893724744</v>
       </c>
       <c r="D87">
-        <v>6.677870828615755</v>
+        <v>6.678797893724742</v>
       </c>
       <c r="E87">
-        <v>15.045</v>
+        <v>15.222</v>
       </c>
       <c r="F87">
-        <v>15.045</v>
+        <v>15.222</v>
       </c>
       <c r="G87">
         <v>11.1</v>
@@ -8415,28 +8415,28 @@
         <v>4.074</v>
       </c>
       <c r="M87">
-        <v>0.8319884999999999</v>
+        <v>0.8417766</v>
       </c>
       <c r="N87">
-        <v>3.2420115</v>
+        <v>3.2322234</v>
       </c>
       <c r="O87">
-        <v>0.51872184</v>
+        <v>0.517155744</v>
       </c>
       <c r="P87">
-        <v>2.72328966</v>
+        <v>2.715067656</v>
       </c>
       <c r="Q87">
-        <v>2.86928966</v>
+        <v>2.861067655999999</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.2568698122080482</v>
+        <v>0.2715274380558294</v>
       </c>
       <c r="T87">
-        <v>2.905455412772818</v>
+        <v>3.107223149770931</v>
       </c>
       <c r="U87">
         <v>0.0553</v>
@@ -8453,7 +8453,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>4.896702298168785</v>
+        <v>4.839763899352868</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8461,22 +8461,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.07796256132781612</v>
+        <v>0.07791045082442499</v>
       </c>
       <c r="C88">
-        <v>2.556797893724744</v>
+        <v>2.380725216271786</v>
       </c>
       <c r="D88">
-        <v>6.678797893724742</v>
+        <v>6.679725216271786</v>
       </c>
       <c r="E88">
-        <v>15.222</v>
+        <v>15.399</v>
       </c>
       <c r="F88">
-        <v>15.222</v>
+        <v>15.399</v>
       </c>
       <c r="G88">
         <v>11.1</v>
@@ -8497,28 +8497,28 @@
         <v>4.074</v>
       </c>
       <c r="M88">
-        <v>0.8417766</v>
+        <v>0.8515647</v>
       </c>
       <c r="N88">
-        <v>3.2322234</v>
+        <v>3.2224353</v>
       </c>
       <c r="O88">
-        <v>0.517155744</v>
+        <v>0.515589648</v>
       </c>
       <c r="P88">
-        <v>2.715067656</v>
+        <v>2.706845652</v>
       </c>
       <c r="Q88">
-        <v>2.861067655999999</v>
+        <v>2.852845652</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.2715274380558294</v>
+        <v>0.2884400832648076</v>
       </c>
       <c r="T88">
-        <v>3.107223149770931</v>
+        <v>3.340032077076446</v>
       </c>
       <c r="U88">
         <v>0.0553</v>
@@ -8535,7 +8535,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>4.839763899352868</v>
+        <v>4.784134429245364</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8543,22 +8543,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.07791045082442499</v>
+        <v>0.07785834032103386</v>
       </c>
       <c r="C89">
-        <v>2.380725216271786</v>
+        <v>2.204652796364135</v>
       </c>
       <c r="D89">
-        <v>6.679725216271786</v>
+        <v>6.680652796364135</v>
       </c>
       <c r="E89">
-        <v>15.399</v>
+        <v>15.576</v>
       </c>
       <c r="F89">
-        <v>15.399</v>
+        <v>15.576</v>
       </c>
       <c r="G89">
         <v>11.1</v>
@@ -8579,28 +8579,28 @@
         <v>4.074</v>
       </c>
       <c r="M89">
-        <v>0.8515647</v>
+        <v>0.8613527999999999</v>
       </c>
       <c r="N89">
-        <v>3.2224353</v>
+        <v>3.2126472</v>
       </c>
       <c r="O89">
-        <v>0.515589648</v>
+        <v>0.5140235520000001</v>
       </c>
       <c r="P89">
-        <v>2.706845652</v>
+        <v>2.698623648</v>
       </c>
       <c r="Q89">
-        <v>2.852845652</v>
+        <v>2.844623648</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.2884400832648076</v>
+        <v>0.3081715026752822</v>
       </c>
       <c r="T89">
-        <v>3.340032077076446</v>
+        <v>3.611642492266212</v>
       </c>
       <c r="U89">
         <v>0.0553</v>
@@ -8617,7 +8617,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>4.784134429245364</v>
+        <v>4.729769265276667</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8625,22 +8625,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.07785834032103386</v>
+        <v>0.07780622981764274</v>
       </c>
       <c r="C90">
-        <v>2.204652796364135</v>
+        <v>2.028580634109098</v>
       </c>
       <c r="D90">
-        <v>6.680652796364135</v>
+        <v>6.681580634109096</v>
       </c>
       <c r="E90">
-        <v>15.576</v>
+        <v>15.753</v>
       </c>
       <c r="F90">
-        <v>15.576</v>
+        <v>15.753</v>
       </c>
       <c r="G90">
         <v>11.1</v>
@@ -8661,28 +8661,28 @@
         <v>4.074</v>
       </c>
       <c r="M90">
-        <v>0.8613527999999999</v>
+        <v>0.8711409</v>
       </c>
       <c r="N90">
-        <v>3.2126472</v>
+        <v>3.2028591</v>
       </c>
       <c r="O90">
-        <v>0.5140235520000001</v>
+        <v>0.512457456</v>
       </c>
       <c r="P90">
-        <v>2.698623648</v>
+        <v>2.690401644</v>
       </c>
       <c r="Q90">
-        <v>2.844623648</v>
+        <v>2.836401644</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.3081715026752822</v>
+        <v>0.3314904528876613</v>
       </c>
       <c r="T90">
-        <v>3.611642492266212</v>
+        <v>3.932636619308664</v>
       </c>
       <c r="U90">
         <v>0.0553</v>
@@ -8699,7 +8699,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>4.729769265276667</v>
+        <v>4.676625790385918</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8707,22 +8707,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.07780622981764274</v>
+        <v>0.07775411931425161</v>
       </c>
       <c r="C91">
-        <v>2.028580634109098</v>
+        <v>1.852508729614037</v>
       </c>
       <c r="D91">
-        <v>6.681580634109096</v>
+        <v>6.682508729614035</v>
       </c>
       <c r="E91">
-        <v>15.753</v>
+        <v>15.93</v>
       </c>
       <c r="F91">
-        <v>15.753</v>
+        <v>15.93</v>
       </c>
       <c r="G91">
         <v>11.1</v>
@@ -8743,28 +8743,28 @@
         <v>4.074</v>
       </c>
       <c r="M91">
-        <v>0.8711409</v>
+        <v>0.880929</v>
       </c>
       <c r="N91">
-        <v>3.2028591</v>
+        <v>3.193071</v>
       </c>
       <c r="O91">
-        <v>0.512457456</v>
+        <v>0.51089136</v>
       </c>
       <c r="P91">
-        <v>2.690401644</v>
+        <v>2.68217964</v>
       </c>
       <c r="Q91">
-        <v>2.836401644</v>
+        <v>2.82817964</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.3314904528876613</v>
+        <v>0.3594731931425162</v>
       </c>
       <c r="T91">
-        <v>3.932636619308664</v>
+        <v>4.317829571759607</v>
       </c>
       <c r="U91">
         <v>0.0553</v>
@@ -8781,7 +8781,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>4.676625790385918</v>
+        <v>4.624663281603852</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8789,22 +8789,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.07775411931425161</v>
+        <v>0.07770200881086048</v>
       </c>
       <c r="C92">
-        <v>1.852508729614037</v>
+        <v>1.676437082986379</v>
       </c>
       <c r="D92">
-        <v>6.682508729614035</v>
+        <v>6.683437082986379</v>
       </c>
       <c r="E92">
-        <v>15.93</v>
+        <v>16.107</v>
       </c>
       <c r="F92">
-        <v>15.93</v>
+        <v>16.107</v>
       </c>
       <c r="G92">
         <v>11.1</v>
@@ -8825,28 +8825,28 @@
         <v>4.074</v>
       </c>
       <c r="M92">
-        <v>0.880929</v>
+        <v>0.8907171</v>
       </c>
       <c r="N92">
-        <v>3.193071</v>
+        <v>3.1832829</v>
       </c>
       <c r="O92">
-        <v>0.51089136</v>
+        <v>0.509325264</v>
       </c>
       <c r="P92">
-        <v>2.68217964</v>
+        <v>2.673957636</v>
       </c>
       <c r="Q92">
-        <v>2.82817964</v>
+        <v>2.819957636</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.3594731931425162</v>
+        <v>0.3936743201206722</v>
       </c>
       <c r="T92">
-        <v>4.317829571759607</v>
+        <v>4.788620958088536</v>
       </c>
       <c r="U92">
         <v>0.0553</v>
@@ -8863,7 +8863,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>4.624663281603852</v>
+        <v>4.573842805981831</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8871,22 +8871,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.07770200881086048</v>
+        <v>0.07764989830746936</v>
       </c>
       <c r="C93">
-        <v>1.676437082986379</v>
+        <v>1.500365694333617</v>
       </c>
       <c r="D93">
-        <v>6.683437082986379</v>
+        <v>6.684365694333615</v>
       </c>
       <c r="E93">
-        <v>16.107</v>
+        <v>16.284</v>
       </c>
       <c r="F93">
-        <v>16.107</v>
+        <v>16.284</v>
       </c>
       <c r="G93">
         <v>11.1</v>
@@ -8907,28 +8907,28 @@
         <v>4.074</v>
       </c>
       <c r="M93">
-        <v>0.8907171</v>
+        <v>0.9005052</v>
       </c>
       <c r="N93">
-        <v>3.1832829</v>
+        <v>3.1734948</v>
       </c>
       <c r="O93">
-        <v>0.509325264</v>
+        <v>0.507759168</v>
       </c>
       <c r="P93">
-        <v>2.673957636</v>
+        <v>2.665735632</v>
       </c>
       <c r="Q93">
-        <v>2.819957636</v>
+        <v>2.811735632</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.3936743201206722</v>
+        <v>0.4364257288433672</v>
       </c>
       <c r="T93">
-        <v>4.788620958088536</v>
+        <v>5.377110190999699</v>
       </c>
       <c r="U93">
         <v>0.0553</v>
@@ -8945,7 +8945,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>4.573842805981831</v>
+        <v>4.524127123308116</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8953,22 +8953,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.07764989830746936</v>
+        <v>0.07955078780407823</v>
       </c>
       <c r="C94">
-        <v>1.500365694333617</v>
+        <v>1.289657900135815</v>
       </c>
       <c r="D94">
-        <v>6.684365694333615</v>
+        <v>6.650657900135814</v>
       </c>
       <c r="E94">
-        <v>16.284</v>
+        <v>16.461</v>
       </c>
       <c r="F94">
-        <v>16.284</v>
+        <v>16.461</v>
       </c>
       <c r="G94">
         <v>11.1</v>
@@ -8989,45 +8989,45 @@
         <v>4.074</v>
       </c>
       <c r="M94">
-        <v>0.9005052</v>
+        <v>0.9514458</v>
       </c>
       <c r="N94">
-        <v>3.1734948</v>
+        <v>3.1225542</v>
       </c>
       <c r="O94">
-        <v>0.507759168</v>
+        <v>0.499608672</v>
       </c>
       <c r="P94">
-        <v>2.665735632</v>
+        <v>2.622945528</v>
       </c>
       <c r="Q94">
-        <v>2.811735632</v>
+        <v>2.768945528</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.4364257288433672</v>
+        <v>0.4913918257725465</v>
       </c>
       <c r="T94">
-        <v>5.377110190999699</v>
+        <v>6.133739204742621</v>
       </c>
       <c r="U94">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="V94">
         <v>0.16</v>
       </c>
       <c r="W94">
-        <v>0.046452</v>
+        <v>0.048552</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y94">
-        <v>4.524127123308116</v>
+        <v>4.281904444793387</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9035,22 +9035,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.07955078780407823</v>
+        <v>0.07951967730068711</v>
       </c>
       <c r="C95">
-        <v>1.289657900135815</v>
+        <v>1.11320683492178</v>
       </c>
       <c r="D95">
-        <v>6.650657900135814</v>
+        <v>6.65120683492178</v>
       </c>
       <c r="E95">
-        <v>16.461</v>
+        <v>16.638</v>
       </c>
       <c r="F95">
-        <v>16.461</v>
+        <v>16.638</v>
       </c>
       <c r="G95">
         <v>11.1</v>
@@ -9071,28 +9071,28 @@
         <v>4.074</v>
       </c>
       <c r="M95">
-        <v>0.9514458</v>
+        <v>0.9616764000000002</v>
       </c>
       <c r="N95">
-        <v>3.1225542</v>
+        <v>3.1123236</v>
       </c>
       <c r="O95">
-        <v>0.499608672</v>
+        <v>0.497971776</v>
       </c>
       <c r="P95">
-        <v>2.622945528</v>
+        <v>2.614351824</v>
       </c>
       <c r="Q95">
-        <v>2.768945528</v>
+        <v>2.760351824</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.4913918257725465</v>
+        <v>0.5646799550114523</v>
       </c>
       <c r="T95">
-        <v>6.133739204742621</v>
+        <v>7.142577889733187</v>
       </c>
       <c r="U95">
         <v>0.0578</v>
@@ -9109,7 +9109,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>4.281904444793387</v>
+        <v>4.236352269848776</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9117,22 +9117,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.07951967730068711</v>
+        <v>0.07948856679729599</v>
       </c>
       <c r="C96">
-        <v>1.11320683492178</v>
+        <v>0.9367558603316439</v>
       </c>
       <c r="D96">
-        <v>6.65120683492178</v>
+        <v>6.651755860331645</v>
       </c>
       <c r="E96">
-        <v>16.638</v>
+        <v>16.815</v>
       </c>
       <c r="F96">
-        <v>16.638</v>
+        <v>16.815</v>
       </c>
       <c r="G96">
         <v>11.1</v>
@@ -9153,28 +9153,28 @@
         <v>4.074</v>
       </c>
       <c r="M96">
-        <v>0.9616764000000002</v>
+        <v>0.9719070000000002</v>
       </c>
       <c r="N96">
-        <v>3.1123236</v>
+        <v>3.102093</v>
       </c>
       <c r="O96">
-        <v>0.497971776</v>
+        <v>0.4963348799999999</v>
       </c>
       <c r="P96">
-        <v>2.614351824</v>
+        <v>2.60575812</v>
       </c>
       <c r="Q96">
-        <v>2.760351824</v>
+        <v>2.751758119999999</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>0.5646799550114523</v>
+        <v>0.6672833359459206</v>
       </c>
       <c r="T96">
-        <v>7.142577889733187</v>
+        <v>8.554952048719979</v>
       </c>
       <c r="U96">
         <v>0.0578</v>
@@ -9191,7 +9191,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>4.236352269848776</v>
+        <v>4.191759088060893</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9199,22 +9199,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.07948856679729599</v>
+        <v>0.07945745629390485</v>
       </c>
       <c r="C97">
-        <v>0.9367558603316439</v>
+        <v>0.7603049763878502</v>
       </c>
       <c r="D97">
-        <v>6.651755860331645</v>
+        <v>6.652304976387852</v>
       </c>
       <c r="E97">
-        <v>16.815</v>
+        <v>16.992</v>
       </c>
       <c r="F97">
-        <v>16.815</v>
+        <v>16.992</v>
       </c>
       <c r="G97">
         <v>11.1</v>
@@ -9235,28 +9235,28 @@
         <v>4.074</v>
       </c>
       <c r="M97">
-        <v>0.9719070000000002</v>
+        <v>0.9821376000000002</v>
       </c>
       <c r="N97">
-        <v>3.102093</v>
+        <v>3.0918624</v>
       </c>
       <c r="O97">
-        <v>0.4963348799999999</v>
+        <v>0.494697984</v>
       </c>
       <c r="P97">
-        <v>2.60575812</v>
+        <v>2.597164416</v>
       </c>
       <c r="Q97">
-        <v>2.751758119999999</v>
+        <v>2.743164415999999</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>0.6672833359459206</v>
+        <v>0.821188407347623</v>
       </c>
       <c r="T97">
-        <v>8.554952048719979</v>
+        <v>10.67351328720017</v>
       </c>
       <c r="U97">
         <v>0.0578</v>
@@ -9273,7 +9273,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>4.191759088060893</v>
+        <v>4.148094930893593</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9281,22 +9281,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.07945745629390488</v>
+        <v>0.07942634579051375</v>
       </c>
       <c r="C98">
-        <v>0.7603049763878538</v>
+        <v>0.5838541831128481</v>
       </c>
       <c r="D98">
-        <v>6.652304976387851</v>
+        <v>6.65285418311285</v>
       </c>
       <c r="E98">
-        <v>16.992</v>
+        <v>17.169</v>
       </c>
       <c r="F98">
-        <v>16.992</v>
+        <v>17.169</v>
       </c>
       <c r="G98">
         <v>11.1</v>
@@ -9317,28 +9317,28 @@
         <v>4.074</v>
       </c>
       <c r="M98">
-        <v>0.9821375999999999</v>
+        <v>0.9923682000000001</v>
       </c>
       <c r="N98">
-        <v>3.0918624</v>
+        <v>3.0816318</v>
       </c>
       <c r="O98">
-        <v>0.494697984</v>
+        <v>0.493061088</v>
       </c>
       <c r="P98">
-        <v>2.597164416</v>
+        <v>2.588570712</v>
       </c>
       <c r="Q98">
-        <v>2.743164416</v>
+        <v>2.734570712</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>0.821188407347621</v>
+        <v>1.077696859683791</v>
       </c>
       <c r="T98">
-        <v>10.67351328720014</v>
+        <v>14.2044486846671</v>
       </c>
       <c r="U98">
         <v>0.0578</v>
@@ -9355,7 +9355,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>4.148094930893594</v>
+        <v>4.105331065626649</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9363,22 +9363,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.07942634579051375</v>
+        <v>0.07939523528712261</v>
       </c>
       <c r="C99">
-        <v>0.5838541831128481</v>
+        <v>0.4074034805291014</v>
       </c>
       <c r="D99">
-        <v>6.65285418311285</v>
+        <v>6.653403480529102</v>
       </c>
       <c r="E99">
-        <v>17.169</v>
+        <v>17.346</v>
       </c>
       <c r="F99">
-        <v>17.169</v>
+        <v>17.346</v>
       </c>
       <c r="G99">
         <v>11.1</v>
@@ -9399,28 +9399,28 @@
         <v>4.074</v>
       </c>
       <c r="M99">
-        <v>0.9923682000000001</v>
+        <v>1.0025988</v>
       </c>
       <c r="N99">
-        <v>3.0816318</v>
+        <v>3.071401199999999</v>
       </c>
       <c r="O99">
-        <v>0.493061088</v>
+        <v>0.4914241919999999</v>
       </c>
       <c r="P99">
-        <v>2.588570712</v>
+        <v>2.579977008</v>
       </c>
       <c r="Q99">
-        <v>2.734570712</v>
+        <v>2.725977008</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>1.077696859683791</v>
+        <v>1.590713764356129</v>
       </c>
       <c r="T99">
-        <v>14.2044486846671</v>
+        <v>21.26631947960103</v>
       </c>
       <c r="U99">
         <v>0.0578</v>
@@ -9437,7 +9437,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>4.105331065626649</v>
+        <v>4.063439932303927</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9445,22 +9445,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.07939523528712261</v>
+        <v>0.07936412478373149</v>
       </c>
       <c r="C100">
-        <v>0.4074034805291014</v>
+        <v>0.2309528686590703</v>
       </c>
       <c r="D100">
-        <v>6.653403480529102</v>
+        <v>6.653952868659069</v>
       </c>
       <c r="E100">
-        <v>17.346</v>
+        <v>17.523</v>
       </c>
       <c r="F100">
-        <v>17.346</v>
+        <v>17.523</v>
       </c>
       <c r="G100">
         <v>11.1</v>
@@ -9481,28 +9481,28 @@
         <v>4.074</v>
       </c>
       <c r="M100">
-        <v>1.0025988</v>
+        <v>1.0128294</v>
       </c>
       <c r="N100">
-        <v>3.071401199999999</v>
+        <v>3.0611706</v>
       </c>
       <c r="O100">
-        <v>0.4914241919999999</v>
+        <v>0.4897872959999999</v>
       </c>
       <c r="P100">
-        <v>2.579977008</v>
+        <v>2.571383304</v>
       </c>
       <c r="Q100">
-        <v>2.725977008</v>
+        <v>2.717383304</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>1.590713764356129</v>
+        <v>3.129764478373146</v>
       </c>
       <c r="T100">
-        <v>21.26631947960103</v>
+        <v>42.45193186440282</v>
       </c>
       <c r="U100">
         <v>0.0578</v>
@@ -9519,91 +9519,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>4.063439932303927</v>
+        <v>4.022395084502879</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.07936412478373149</v>
-      </c>
-      <c r="C101">
-        <v>0.2309528686590703</v>
-      </c>
-      <c r="D101">
-        <v>6.653952868659069</v>
-      </c>
-      <c r="E101">
-        <v>17.523</v>
-      </c>
-      <c r="F101">
-        <v>17.523</v>
-      </c>
-      <c r="G101">
-        <v>11.1</v>
-      </c>
-      <c r="H101">
-        <v>17.7</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>4.22</v>
-      </c>
-      <c r="K101">
-        <v>0.146</v>
-      </c>
-      <c r="L101">
-        <v>4.074</v>
-      </c>
-      <c r="M101">
-        <v>1.0128294</v>
-      </c>
-      <c r="N101">
-        <v>3.0611706</v>
-      </c>
-      <c r="O101">
-        <v>0.4897872959999999</v>
-      </c>
-      <c r="P101">
-        <v>2.571383304</v>
-      </c>
-      <c r="Q101">
-        <v>2.717383304</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>3.129764478373146</v>
-      </c>
-      <c r="T101">
-        <v>42.45193186440282</v>
-      </c>
-      <c r="U101">
-        <v>0.0578</v>
-      </c>
-      <c r="V101">
-        <v>0.16</v>
-      </c>
-      <c r="W101">
-        <v>0.048552</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>Baa2/BBB</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>4.022395084502879</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
